--- a/Text2SQL_Template/output/ddq_autogen_transaction.xlsx
+++ b/Text2SQL_Template/output/ddq_autogen_transaction.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\proton-intern\javisAI\6804_ddq\Text2SQL_Template\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF8525B-E4EC-42D4-95FB-215C8E8D3678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -562,256 +568,1881 @@
     <t>Tìm kiếm chính xác bản ghi dựa trên from_cif_no</t>
   </si>
   <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{reference_id}}}|Hiển thị lệnh chuyển tiền mang id {{{reference_id}}}|Xem chi tiết biến động số dư theo primary key {{{reference_id}}}|Search giao dịch của mã {{{reference_id}}}|Liệt kê biến động số dư của khóa chính {{{reference_id}}}|Kiểm tra biến động số dư với id {{{reference_id}}}|Hiển thị biến động số dư với id {{{reference_id}}}|Xem chi tiết history tại primary key {{{reference_id}}}|Liệt kê lệnh chuyển tiền tại khóa chính {{{reference_id}}}|Tra cứu biến động số dư với id {{{reference_id}}}|Liệt kê lệnh chuyển tiền với số {{{reference_id}}}|Liệt kê history của mã {{{reference_id}}}|Tìm biến động số dư theo primary key {{{reference_id}}}|Cho tôi xem giao dịch có số {{{reference_id}}}|Kiểm tra biến động số dư tại mã {{{reference_id}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{trans_id}}}|Liệt kê biến động số dư của có thể tra soát {{{trans_id}}}|Hiển thị lệnh chuyển tiền mang id {{{trans_id}}}|Tra cứu giao dịch với mã định danh giao dịch theo nghiệp vụ, phân biệt các giao dịch với nhau {{{trans_id}}}|Xem chi tiết giao dịch với có thể tra soát {{{trans_id}}}|Search giao dịch của mã {{{trans_id}}}|Kiểm tra biến động số dư với id {{{trans_id}}}|Hiển thị biến động số dư với id {{{trans_id}}}|Kiểm tra lệnh chuyển tiền với mã định danh giao dịch theo nghiệp vụ, phân biệt các giao dịch với nhau {{{trans_id}}}|Cho tôi xem history của mã định danh giao dịch theo nghiệp vụ, phân biệt các giao dịch với nhau {{{trans_id}}}|Tra cứu giao dịch có có thể tra soát {{{trans_id}}}|Tra cứu biến động số dư với id {{{trans_id}}}|Liệt kê lệnh chuyển tiền với số {{{trans_id}}}|Liệt kê history của mã {{{trans_id}}}|Hiển thị lệnh chuyển tiền tại có thể tra soát {{{trans_id}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị lệnh chuyển tiền với ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Tra cứu history có mã loại hình giao dịch {{{trans_code}}}|Tra cứu lệnh chuyển tiền với mã loại hình giao dịch {{{trans_code}}}|Liệt kê history có ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Tìm lệnh chuyển tiền tại ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Liệt kê history theo ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Hiển thị history theo ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Liệt kê lệnh chuyển tiền theo ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Cho tôi xem biến động số dư với ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Cho tôi xem history theo ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Tìm biến động số dư có ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Tra cứu lệnh chuyển tiền có ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Hiển thị giao dịch mang ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}|Hiển thị lệnh chuyển tiền của mã loại hình giao dịch {{{trans_code}}}|Liệt kê giao dịch với mã loại hình giao dịch {{{trans_code}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{parent_id}}}|Kiểm tra biến động số dư mang id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp. {{{parent_id}}}|Kiểm tra biến động số dư của id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp. {{{parent_id}}}|Hiển thị lệnh chuyển tiền mang id {{{parent_id}}}|Search giao dịch của mã {{{parent_id}}}|Kiểm tra biến động số dư với id {{{parent_id}}}|Hiển thị biến động số dư với id {{{parent_id}}}|Liệt kê lệnh chuyển tiền theo id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp. {{{parent_id}}}|Tra cứu biến động số dư với id {{{parent_id}}}|Liệt kê lệnh chuyển tiền với số {{{parent_id}}}|Liệt kê history của mã {{{parent_id}}}|Search giao dịch có id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp. {{{parent_id}}}|Cho tôi xem giao dịch có số {{{parent_id}}}|Kiểm tra biến động số dư tại mã {{{parent_id}}}|Search biến động số dư theo mã {{{parent_id}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{node_id}}}|Hiển thị lệnh chuyển tiền mang id {{{node_id}}}|Search giao dịch của mã {{{node_id}}}|Kiểm tra biến động số dư có mã định danh node {{{node_id}}}|Kiểm tra biến động số dư với id {{{node_id}}}|Liệt kê lệnh chuyển tiền với máy chủ hoặc phân vùng dữ liệu {{{node_id}}}|Hiển thị biến động số dư với id {{{node_id}}}|Cho tôi xem giao dịch tại máy chủ hoặc phân vùng dữ liệu {{{node_id}}}|Kiểm tra history theo máy chủ hoặc phân vùng dữ liệu {{{node_id}}}|Tra cứu biến động số dư với id {{{node_id}}}|Liệt kê lệnh chuyển tiền với số {{{node_id}}}|Liệt kê history của mã {{{node_id}}}|Tìm biến động số dư có máy chủ hoặc phân vùng dữ liệu {{{node_id}}}|Cho tôi xem giao dịch có số {{{node_id}}}|Kiểm tra biến động số dư tại mã {{{node_id}}}</t>
-  </si>
-  <si>
-    <t>Tìm biến động số dư của mã định danh {{{user_id}}}|Hiển thị lệnh chuyển tiền mang id {{{user_id}}}|Kiểm tra biến động số dư theo khách hàng {{{user_id}}}|Tra cứu biến động số dư với id {{{user_id}}}|Hiển thị biến động số dư mang thường khóa ngoại trỏ sang bảng user {{{user_id}}}|Liệt kê history của mã {{{user_id}}}|Tìm biến động số dư theo mã định danh {{{user_id}}}|Cho tôi xem giao dịch có số {{{user_id}}}|Liệt kê history của mã định danh {{{user_id}}}|Tra cứu giao dịch của khách hàng {{{user_id}}}|Search lệnh chuyển tiền mang mã {{{user_id}}}|Hiển thị biến động số dư theo thường khóa ngoại trỏ sang bảng user {{{user_id}}}|Liệt kê lệnh chuyển tiền tại mã {{{user_id}}}|Liệt kê history có khách hàng {{{user_id}}}|Tra cứu history mang số {{{user_id}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết giao dịch mang web/app session {{{session_id}}}|Tìm biến động số dư theo session {{{session_id}}}|Kiểm tra lệnh chuyển tiền với mã {{{session_id}}}|Hiển thị lệnh chuyển tiền mang id {{{session_id}}}|Liệt kê lệnh chuyển tiền tại session {{{session_id}}}|Search giao dịch của mã {{{session_id}}}|Tìm history với web/app session {{{session_id}}}|Kiểm tra biến động số dư với id {{{session_id}}}|Hiển thị biến động số dư với id {{{session_id}}}|Cho tôi xem lệnh chuyển tiền theo session {{{session_id}}}|Kiểm tra biến động số dư theo session {{{session_id}}}|Tra cứu giao dịch mang web/app session {{{session_id}}}|Tra cứu biến động số dư với id {{{session_id}}}|Liệt kê lệnh chuyển tiền với số {{{session_id}}}|Liệt kê history của mã {{{session_id}}}</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch từ ngày {{start_date}} đến {{end_date}}|Liệt kê lịch sử trong khoảng thời gian {{start_date}} - {{end_date}}|Kiểm tra giao dịch phát sinh từ {{start_date}} tới {{end_date}}|Cho tôi xem biến động số dư giữa {{start_date}} và {{end_date}}</t>
-  </si>
-  <si>
-    <t>Những history có loại {{{trans_type}}}|Danh sách history của loại {{{trans_type}}}|Danh sách lệnh chuyển tiền theo hình thức {{{trans_type}}}|Danh sách history với hình thức {{{trans_type}}}|Danh sách lệnh chuyển tiền với loại {{{trans_type}}}|Các biến động số dư theo loại {{{trans_type}}}|Danh sách giao dịch với loại giao dịch chi tiết hoặc mô tả nhóm giao dịch. {{{trans_type}}}|Danh sách lệnh chuyển tiền mang hình thức {{{trans_type}}}|Danh sách lệnh chuyển tiền có hình thức {{{trans_type}}}|Danh sách history của hình thức {{{trans_type}}}|Danh sách biến động số dư theo loại {{{trans_type}}}|Lọc các history mang loại {{{trans_type}}}|Các giao dịch của loại {{{trans_type}}}|Các lệnh chuyển tiền có loại giao dịch chi tiết hoặc mô tả nhóm giao dịch. {{{trans_type}}}|Danh sách giao dịch mang hình thức {{{trans_type}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{action_id}}}|Hiển thị lệnh chuyển tiền mang id {{{action_id}}}|Search giao dịch của mã {{{action_id}}}|Kiểm tra biến động số dư với id {{{action_id}}}|Hiển thị biến động số dư với id {{{action_id}}}|Xem chi tiết biến động số dư có ví dụ: nút bấm "xác nhận", "gửi otp" {{{action_id}}}|Xem chi tiết lệnh chuyển tiền tại ví dụ: nút bấm "xác nhận", "gửi otp" {{{action_id}}}|Tra cứu biến động số dư với id {{{action_id}}}|Hiển thị biến động số dư với mã hành động cụ thể mà thực hiện {{{action_id}}}|Liệt kê lệnh chuyển tiền với số {{{action_id}}}|Liệt kê history của mã {{{action_id}}}|Cho tôi xem giao dịch có số {{{action_id}}}|Kiểm tra biến động số dư tại mã {{{action_id}}}|Liệt kê giao dịch mang mã hành động cụ thể mà thực hiện {{{action_id}}}|Search biến động số dư theo mã {{{action_id}}}</t>
-  </si>
-  <si>
-    <t>Những biến động số dư theo kênh {{{channel_receiver}}}|Danh sách biến động số dư có kênh tiếp nhận giao dịch {{{channel_receiver}}}|Các history mang kênh {{{channel_receiver}}}|Các history tại ví dụ: mobile app, internet banking, atm, counter {{{channel_receiver}}}|Những giao dịch tại kênh tiếp nhận giao dịch {{{channel_receiver}}}|Danh sách lệnh chuyển tiền có nguồn {{{channel_receiver}}}|Các giao dịch có kênh {{{channel_receiver}}}|Danh sách history mang kênh {{{channel_receiver}}}|Danh sách lệnh chuyển tiền theo ví dụ: mobile app, internet banking, atm, counter {{{channel_receiver}}}|Các lệnh chuyển tiền với kênh {{{channel_receiver}}}|Các biến động số dư mang nguồn {{{channel_receiver}}}|Danh sách lệnh chuyển tiền với ví dụ: mobile app, internet banking, atm, counter {{{channel_receiver}}}|Những history của nguồn {{{channel_receiver}}}|Lọc các biến động số dư của kênh tiếp nhận giao dịch {{{channel_receiver}}}|Các biến động số dư mang kênh {{{channel_receiver}}}</t>
-  </si>
-  <si>
-    <t>Danh sách lệnh chuyển tiền theo hình thức {{{stak_user_type_do}}}|Các history mang khách hàng {{{stak_user_type_do}}}|Danh sách biến động số dư theo loại {{{stak_user_type_do}}}|Danh sách lệnh chuyển tiền tại thường cho nhân viên vận hành/digital officer {{{stak_user_type_do}}}|Danh sách giao dịch mang loại tác nghiệp {{{stak_user_type_do}}}|Những biến động số dư theo loại tác nghiệp {{{stak_user_type_do}}}|Lọc các history với khách hàng {{{stak_user_type_do}}}|Các lệnh chuyển tiền theo hình thức {{{stak_user_type_do}}}|Lọc các biến động số dư của người dùng {{{stak_user_type_do}}}|Danh sách giao dịch có hình thức {{{stak_user_type_do}}}|Danh sách giao dịch tại hình thức {{{stak_user_type_do}}}|Các giao dịch với hình thức {{{stak_user_type_do}}}|Các giao dịch với thường cho nhân viên vận hành/digital officer {{{stak_user_type_do}}}|Lọc các giao dịch theo thường cho nhân viên vận hành/digital officer {{{stak_user_type_do}}}|Các giao dịch tại người dùng {{{stak_user_type_do}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết giao dịch có người dùng {{{user_do}}}|Search lệnh chuyển tiền theo người dùng {{{user_do}}}|Tra cứu biến động số dư tại người dùng {{{user_do}}}|Cho tôi xem biến động số dư có nếu có {{{user_do}}}|Kiểm tra biến động số dư theo khách hàng {{{user_do}}}|Tra cứu history theo khách hàng {{{user_do}}}|Xem chi tiết biến động số dư theo tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này {{{user_do}}}|Xem chi tiết giao dịch có nếu có {{{user_do}}}|nếu có {{{user_do}}} là bao nhiêu|Xem chi tiết lệnh chuyển tiền theo nếu có {{{user_do}}}|Cho tôi xem giao dịch với tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này {{{user_do}}}|Tìm history tại khách hàng {{{user_do}}}|Liệt kê lệnh chuyển tiền theo nếu có {{{user_do}}}|Tìm giao dịch mang khách hàng {{{user_do}}}|Tra cứu giao dịch của khách hàng {{{user_do}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị giao dịch có mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Hiển thị giao dịch với mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Hiển thị history mang digital office branch {{{branch_code_do}}}|Tra cứu biến động số dư mang mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Tìm biến động số dư theo mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Hiển thị giao dịch tại digital office branch {{{branch_code_do}}}|Cho tôi xem history mang digital office branch {{{branch_code_do}}}|Tìm history có mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Search lệnh chuyển tiền của digital office branch {{{branch_code_do}}}|Xem chi tiết biến động số dư tại mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Liệt kê giao dịch có digital office branch {{{branch_code_do}}}|Cho tôi xem history theo digital office branch {{{branch_code_do}}}|Kiểm tra history với mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Hiển thị history của mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}|Liệt kê history với mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}</t>
-  </si>
-  <si>
-    <t>Search lệnh chuyển tiền của ví dụ: gói tài khoản, gói vay {{{product_id}}}|Kiểm tra lệnh chuyển tiền với mã {{{product_id}}}|Tìm history với ví dụ: gói tài khoản, gói vay {{{product_id}}}|Cho tôi xem giao dịch theo mã sản phẩm hoặc dịch vụ liên quan đến giao dịch {{{product_id}}}|Hiển thị lệnh chuyển tiền mang id {{{product_id}}}|Search giao dịch của mã {{{product_id}}}|Kiểm tra biến động số dư với id {{{product_id}}}|Hiển thị biến động số dư với id {{{product_id}}}|Xem chi tiết biến động số dư có ví dụ: gói tài khoản, gói vay {{{product_id}}}|Tra cứu biến động số dư với id {{{product_id}}}|Liệt kê lệnh chuyển tiền với số {{{product_id}}}|Xem chi tiết biến động số dư với ví dụ: gói tài khoản, gói vay {{{product_id}}}|Hiển thị lệnh chuyển tiền tại ví dụ: gói tài khoản, gói vay {{{product_id}}}|Liệt kê history của mã {{{product_id}}}|Cho tôi xem giao dịch có số {{{product_id}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{request_id}}}|Hiển thị lệnh chuyển tiền mang id {{{request_id}}}|Search giao dịch của mã {{{request_id}}}|Kiểm tra biến động số dư với id {{{request_id}}}|Hiển thị biến động số dư với id {{{request_id}}}|Tra cứu biến động số dư với id {{{request_id}}}|Liệt kê lệnh chuyển tiền với số {{{request_id}}}|Liệt kê history của mã {{{request_id}}}|Cho tôi xem giao dịch có số {{{request_id}}}|Kiểm tra biến động số dư tại mã {{{request_id}}}|Search biến động số dư theo mã {{{request_id}}}|Tìm giao dịch mang app/web {{{request_id}}}|Search history với mã yêu cầu duy nhất được sinh ra từ phía client {{{request_id}}}|Hiển thị giao dịch mang mã yêu cầu duy nhất được sinh ra từ phía client {{{request_id}}}|Kiểm tra biến động số dư mang id {{{request_id}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{original_request_id}}}|Tìm history của dùng cho các giao dịch hoàn tiền, hủy hoặc đảo giao dịch tham chiếu lại giao dịch cũ {{{original_request_id}}}|Hiển thị lệnh chuyển tiền mang id {{{original_request_id}}}|Xem chi tiết history với mã yêu cầu gốc {{{original_request_id}}}|Liệt kê history với mã yêu cầu gốc {{{original_request_id}}}|Search giao dịch của mã {{{original_request_id}}}|Kiểm tra biến động số dư với id {{{original_request_id}}}|Search biến động số dư có mã yêu cầu gốc {{{original_request_id}}}|Hiển thị biến động số dư với id {{{original_request_id}}}|Kiểm tra biến động số dư của dùng cho các giao dịch hoàn tiền, hủy hoặc đảo giao dịch tham chiếu lại giao dịch cũ {{{original_request_id}}}|Tra cứu biến động số dư với id {{{original_request_id}}}|Hiển thị giao dịch tại mã yêu cầu gốc {{{original_request_id}}}|Liệt kê lệnh chuyển tiền với số {{{original_request_id}}}|Liệt kê history của mã {{{original_request_id}}}|Liệt kê lệnh chuyển tiền theo dùng cho các giao dịch hoàn tiền, hủy hoặc đảo giao dịch tham chiếu lại giao dịch cũ {{{original_request_id}}}</t>
-  </si>
-  <si>
-    <t>Search biến động số dư có loại dữ liệu đầu vào {{{input_type}}}|Xem chi tiết biến động số dư theo loại dữ liệu đầu vào {{{input_type}}}|Kiểm tra history với hình thức {{{input_type}}}|Tra cứu biến động số dư của loại {{{input_type}}}|Search giao dịch có ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}|Xem chi tiết history theo ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}|Liệt kê biến động số dư với loại {{{input_type}}}|Cho tôi xem giao dịch của loại dữ liệu đầu vào {{{input_type}}}|Liệt kê biến động số dư tại loại dữ liệu đầu vào {{{input_type}}}|Tìm history với ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}|Liệt kê giao dịch mang loại {{{input_type}}}|Hiển thị giao dịch theo loại {{{input_type}}}|Xem chi tiết lệnh chuyển tiền của ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}|Hiển thị lệnh chuyển tiền theo ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}|Hiển thị lệnh chuyển tiền của loại {{{input_type}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra biến động số dư theo giá trị đầu vào tương ứng {{{input_value}}}|Search giao dịch có ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}|Hiển thị history có giá trị đầu vào tương ứng {{{input_value}}}|Liệt kê lệnh chuyển tiền mang giá trị đầu vào tương ứng {{{input_value}}}|Cho tôi xem giao dịch của giá trị đầu vào tương ứng {{{input_value}}}|Cho tôi xem giao dịch với ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}|Tìm lệnh chuyển tiền theo giá trị đầu vào tương ứng {{{input_value}}}|Kiểm tra giao dịch của giá trị đầu vào tương ứng {{{input_value}}}|Cho tôi xem biến động số dư mang ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}|Cho tôi xem lệnh chuyển tiền có ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}|Cho tôi xem giao dịch của ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}|Liệt kê giao dịch có ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}|Kiểm tra giao dịch của ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}|Xem chi tiết giao dịch tại giá trị đầu vào tương ứng {{{input_value}}}|Tra cứu biến động số dư theo giá trị đầu vào tương ứng {{{input_value}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{from_system_id}}}|Search history theo nếu giao dịch đến từ đối tác hoặc vệ tinh {{{from_system_id}}}|Xem chi tiết biến động số dư của mã nguồn khởi tạo giao dịch {{{from_system_id}}}|Hiển thị lệnh chuyển tiền mang id {{{from_system_id}}}|Xem chi tiết lệnh chuyển tiền với nếu giao dịch đến từ đối tác hoặc vệ tinh {{{from_system_id}}}|Search giao dịch của mã {{{from_system_id}}}|Kiểm tra biến động số dư với id {{{from_system_id}}}|Kiểm tra lệnh chuyển tiền tại mã nguồn khởi tạo giao dịch {{{from_system_id}}}|Hiển thị lệnh chuyển tiền của nếu giao dịch đến từ đối tác hoặc vệ tinh {{{from_system_id}}}|Hiển thị biến động số dư với id {{{from_system_id}}}|Tra cứu biến động số dư với id {{{from_system_id}}}|Liệt kê lệnh chuyển tiền với số {{{from_system_id}}}|Hiển thị giao dịch của mã nguồn khởi tạo giao dịch {{{from_system_id}}}|Liệt kê history của mã {{{from_system_id}}}|Search biến động số dư mang mã {{{from_system_id}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{from_cust_id}}}|Xem chi tiết history theo id khách hàng chuyển tiền/người thanh toán. {{{from_cust_id}}}|Hiển thị lệnh chuyển tiền mang id {{{from_cust_id}}}|Search giao dịch của mã {{{from_cust_id}}}|Kiểm tra biến động số dư với id {{{from_cust_id}}}|Tra cứu lệnh chuyển tiền có id khách hàng chuyển tiền/người thanh toán. {{{from_cust_id}}}|Hiển thị biến động số dư với id {{{from_cust_id}}}|Tra cứu biến động số dư với id {{{from_cust_id}}}|Liệt kê lệnh chuyển tiền với số {{{from_cust_id}}}|Liệt kê history của mã {{{from_cust_id}}}|Cho tôi xem giao dịch có số {{{from_cust_id}}}|Kiểm tra biến động số dư tại mã {{{from_cust_id}}}|Search biến động số dư theo mã {{{from_cust_id}}}|Kiểm tra biến động số dư mang id {{{from_cust_id}}}|Cho tôi xem history theo id khách hàng chuyển tiền/người thanh toán. {{{from_cust_id}}}</t>
-  </si>
-  <si>
-    <t>Liệt kê history có mã cif {{{from_cust_no}}}|Xem chi tiết lệnh chuyển tiền tại mã cif {{{from_cust_no}}}|Kiểm tra biến động số dư tại customer information file {{{from_cust_no}}}|Hiển thị giao dịch với customer information file {{{from_cust_no}}}|Liệt kê history của mã cif {{{from_cust_no}}}|Kiểm tra biến động số dư có mã cif {{{from_cust_no}}}|Cho tôi xem giao dịch tại customer information file {{{from_cust_no}}}|Kiểm tra biến động số dư của mã cif {{{from_cust_no}}}|Tìm biến động số dư với mã cif {{{from_cust_no}}}|Tra cứu lệnh chuyển tiền của customer information file {{{from_cust_no}}}|Hiển thị history có mã cif {{{from_cust_no}}}|Search biến động số dư theo mã cif {{{from_cust_no}}}|Cho tôi xem giao dịch tại mã cif {{{from_cust_no}}}|Cho tôi xem history mang mã cif {{{from_cust_no}}}|Tra cứu biến động số dư theo mã cif {{{from_cust_no}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết giao dịch có mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Tra cứu biến động số dư mang mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Tìm lệnh chuyển tiền tại mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Xem chi tiết giao dịch với mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Hiển thị biến động số dư có mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Xem chi tiết lệnh chuyển tiền với mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Xem chi tiết history với mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Tra cứu giao dịch của mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Cho tôi xem biến động số dư có mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Liệt kê giao dịch theo mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Search history theo mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Kiểm tra history với mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Cho tôi xem biến động số dư mang mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Liệt kê giao dịch có mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}|Tra cứu giao dịch theo mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}</t>
-  </si>
-  <si>
-    <t>Các giao dịch của hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Lọc các lệnh chuyển tiền với ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}|Danh sách biến động số dư của ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}|Những lệnh chuyển tiền tại ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}|Lọc các giao dịch mang hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Danh sách biến động số dư với hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Những lệnh chuyển tiền có hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Lọc các history tại hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Lọc các lệnh chuyển tiền tại hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Những biến động số dư theo hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Các biến động số dư mang hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Các lệnh chuyển tiền có ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}|Những biến động số dư với hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}|Danh sách giao dịch với ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}|Lọc các biến động số dư theo ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}</t>
-  </si>
-  <si>
-    <t>Những history có loại {{{from_account_type}}}|Danh sách history của loại {{{from_account_type}}}|Danh sách lệnh chuyển tiền theo hình thức {{{from_account_type}}}|Những biến động số dư mang loại tài khoản nguồn chi tiết. {{{from_account_type}}}|Danh sách history với hình thức {{{from_account_type}}}|Danh sách lệnh chuyển tiền với loại {{{from_account_type}}}|Các biến động số dư theo loại {{{from_account_type}}}|Các giao dịch của loại tài khoản nguồn chi tiết. {{{from_account_type}}}|Danh sách lệnh chuyển tiền mang hình thức {{{from_account_type}}}|Các lệnh chuyển tiền tại hình thức {{{from_account_type}}}|Lọc các history theo loại tài khoản nguồn chi tiết. {{{from_account_type}}}|Danh sách lệnh chuyển tiền có hình thức {{{from_account_type}}}|Danh sách history của hình thức {{{from_account_type}}}|Danh sách biến động số dư theo loại {{{from_account_type}}}|Lọc các history mang loại {{{from_account_type}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị giao dịch với tài khoản nguồn {{{from_account_no}}}|Hiển thị biến động số dư của số tài khoản chuyển tiền {{{from_account_no}}}|Search giao dịch của số tài khoản chuyển tiền {{{from_account_no}}}|Hiển thị history tại tài khoản nguồn {{{from_account_no}}}|Cho tôi xem giao dịch tại tài khoản nguồn {{{from_account_no}}}|Hiển thị lệnh chuyển tiền mang tài khoản nguồn {{{from_account_no}}}|Kiểm tra history tại số tài khoản chuyển tiền {{{from_account_no}}}|Search giao dịch theo số tài khoản chuyển tiền {{{from_account_no}}}|Search history với số tài khoản chuyển tiền {{{from_account_no}}}|Cho tôi xem biến động số dư theo số tài khoản chuyển tiền {{{from_account_no}}}|Tra cứu lệnh chuyển tiền theo tài khoản nguồn {{{from_account_no}}}|Tra cứu history của số tài khoản chuyển tiền {{{from_account_no}}}|Cho tôi xem history mang số tài khoản chuyển tiền {{{from_account_no}}}|Tra cứu giao dịch mang tài khoản nguồn {{{from_account_no}}}|Tra cứu history mang tài khoản nguồn {{{from_account_no}}}</t>
-  </si>
-  <si>
-    <t>Cho tôi xem biến động số dư tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Tra cứu biến động số dư theo mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Cho tôi xem history với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Liệt kê biến động số dư mang mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Search history của mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Search history mang mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Tìm history với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Cho tôi xem history tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Search biến động số dư tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Xem chi tiết giao dịch của mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Tra cứu lệnh chuyển tiền với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Xem chi tiết giao dịch với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Hiển thị giao dịch của mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Kiểm tra lệnh chuyển tiền theo mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}|Liệt kê giao dịch tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}</t>
-  </si>
-  <si>
-    <t>Lọc các history có loại tiền tệ tài khoản nguồn {{{from_account_currency}}}|Các biến động số dư của vnd, usd, eur... {{{from_account_currency}}}|Những lệnh chuyển tiền tại vnd, usd, eur... {{{from_account_currency}}}|Lọc các history của loại tiền tệ tài khoản nguồn {{{from_account_currency}}}|Những history tại loại tiền tệ tài khoản nguồn {{{from_account_currency}}}|Những history mang vnd, usd, eur... {{{from_account_currency}}}|Những history có vnd, usd, eur... {{{from_account_currency}}}|Những biến động số dư của vnd, usd, eur... {{{from_account_currency}}}|Những lệnh chuyển tiền của vnd, usd, eur... {{{from_account_currency}}}|Các lệnh chuyển tiền tại vnd, usd, eur... {{{from_account_currency}}}|Danh sách biến động số dư với loại tiền tệ tài khoản nguồn {{{from_account_currency}}}|Những biến động số dư tại loại tiền tệ tài khoản nguồn {{{from_account_currency}}}|Lọc các biến động số dư có loại tiền tệ tài khoản nguồn {{{from_account_currency}}}|Các lệnh chuyển tiền có vnd, usd, eur... {{{from_account_currency}}}|Các giao dịch với loại tiền tệ tài khoản nguồn {{{from_account_currency}}}</t>
-  </si>
-  <si>
-    <t>Các lệnh chuyển tiền có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Những lệnh chuyển tiền của tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Lọc các biến động số dư theo tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Danh sách giao dịch theo tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Lọc các giao dịch mang tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Những giao dịch có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Danh sách history tại tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Danh sách history có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Các giao dịch có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Danh sách lệnh chuyển tiền có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Những lệnh chuyển tiền mang tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Lọc các giao dịch với tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Danh sách history với tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Những biến động số dư mang tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}|Những biến động số dư của tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{to_system_id}}}|Hiển thị lệnh chuyển tiền mang id {{{to_system_id}}}|Hiển thị giao dịch tại mã đích {{{to_system_id}}}|Search giao dịch của mã {{{to_system_id}}}|Tra cứu lệnh chuyển tiền mang nơi nhận tiền/giao dịch {{{to_system_id}}}|Kiểm tra biến động số dư với id {{{to_system_id}}}|Hiển thị giao dịch theo nơi nhận tiền/giao dịch {{{to_system_id}}}|Hiển thị biến động số dư với id {{{to_system_id}}}|Xem chi tiết lệnh chuyển tiền theo nơi nhận tiền/giao dịch {{{to_system_id}}}|Search giao dịch của mã đích {{{to_system_id}}}|Tra cứu biến động số dư với id {{{to_system_id}}}|Liệt kê lệnh chuyển tiền với số {{{to_system_id}}}|Liệt kê history của mã {{{to_system_id}}}|Xem chi tiết lệnh chuyển tiền mang nơi nhận tiền/giao dịch {{{to_system_id}}}|Tra cứu biến động số dư tại mã đích {{{to_system_id}}}</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch với nếu chuyển khoản nội bộ {{{to_cust_no}}}|Tra cứu biến động số dư theo mã khách hàng thụ hưởng {{{to_cust_no}}}|Search history tại mã khách hàng thụ hưởng {{{to_cust_no}}}|Cho tôi xem biến động số dư với nếu chuyển khoản nội bộ {{{to_cust_no}}}|Kiểm tra history của nếu chuyển khoản nội bộ {{{to_cust_no}}}|Cho tôi xem history mang mã khách hàng thụ hưởng {{{to_cust_no}}}|Xem chi tiết giao dịch mang mã khách hàng thụ hưởng {{{to_cust_no}}}|Tra cứu giao dịch của mã khách hàng thụ hưởng {{{to_cust_no}}}|Cho tôi xem history của nếu chuyển khoản nội bộ {{{to_cust_no}}}|Hiển thị biến động số dư với nếu chuyển khoản nội bộ {{{to_cust_no}}}|Xem chi tiết giao dịch của mã khách hàng thụ hưởng {{{to_cust_no}}}|Kiểm tra giao dịch có nếu chuyển khoản nội bộ {{{to_cust_no}}}|mã khách hàng thụ hưởng {{{to_cust_no}}} là bao nhiêu|Search giao dịch của nếu chuyển khoản nội bộ {{{to_cust_no}}}|Xem chi tiết lệnh chuyển tiền có nếu chuyển khoản nội bộ {{{to_cust_no}}}</t>
-  </si>
-  <si>
-    <t>Tìm history của mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Tra cứu history tại mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Tìm lệnh chuyển tiền tại mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Tìm giao dịch mang mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Kiểm tra history với mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Tìm lệnh chuyển tiền theo mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Search lệnh chuyển tiền có mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Search biến động số dư có mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Search biến động số dư với mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Search giao dịch tại mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Cho tôi xem history với mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Tra cứu lệnh chuyển tiền tại mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Hiển thị history theo mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Tra cứu giao dịch mang mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}|Cho tôi xem lệnh chuyển tiền của mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}</t>
-  </si>
-  <si>
-    <t>Liệt kê biến động số dư của số tài khoản nhận tiền {{{to_account_no}}}|Tìm giao dịch mang tài khoản đích {{{to_account_no}}}|Search giao dịch theo tài khoản đích {{{to_account_no}}}|Tìm history có tài khoản đích {{{to_account_no}}}|Search lệnh chuyển tiền tại số tài khoản nhận tiền {{{to_account_no}}}|Search biến động số dư có tài khoản đích {{{to_account_no}}}|Liệt kê giao dịch với tài khoản đích {{{to_account_no}}}|Tìm lệnh chuyển tiền của số tài khoản nhận tiền {{{to_account_no}}}|Tra cứu giao dịch với số tài khoản nhận tiền {{{to_account_no}}}|Tìm giao dịch theo tài khoản đích {{{to_account_no}}}|Hiển thị biến động số dư có tài khoản đích {{{to_account_no}}}|Cho tôi xem lệnh chuyển tiền có tài khoản đích {{{to_account_no}}}|Search biến động số dư của số tài khoản nhận tiền {{{to_account_no}}}|Xem chi tiết lệnh chuyển tiền mang tài khoản đích {{{to_account_no}}}|Hiển thị giao dịch tại tài khoản đích {{{to_account_no}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị giao dịch mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Liệt kê history tại mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Search giao dịch tại mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Tìm biến động số dư tại mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Kiểm tra history mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Kiểm tra biến động số dư mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Search giao dịch mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Search biến động số dư mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Hiển thị biến động số dư với mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Tìm giao dịch mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Xem chi tiết lệnh chuyển tiền có mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Kiểm tra history của mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Tra cứu biến động số dư theo mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Tìm history mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}|Cho tôi xem lệnh chuyển tiền tại mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}</t>
-  </si>
-  <si>
-    <t>Lọc các biến động số dư mang loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Các biến động số dư theo loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Những history của loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Các giao dịch mang loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Các lệnh chuyển tiền với loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Danh sách lệnh chuyển tiền tại loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Những history với loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Các history có loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Lọc các biến động số dư với loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Những lệnh chuyển tiền của loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Những lệnh chuyển tiền với loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Các biến động số dư của loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Danh sách lệnh chuyển tiền có loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Các biến động số dư có loại tiền tệ tài khoản đích. {{{to_account_currency}}}|Những biến động số dư của loại tiền tệ tài khoản đích. {{{to_account_currency}}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}|Tính tổng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}|Tổng cộng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}|Thống kê số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}|Cộng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}|Xem tổng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Lọc các history theo giá trị {{{amount_rate}}}|Các biến động số dư của giá trị {{{amount_rate}}}|Lọc các lệnh chuyển tiền với số tiền {{{amount_rate}}}|Những lệnh chuyển tiền của giá trị {{{amount_rate}}}|Danh sách history với số tiền {{{amount_rate}}}|Những lệnh chuyển tiền theo giá trị {{{amount_rate}}}|Lọc các history mang hạn mức {{{amount_rate}}}|Danh sách giao dịch mang tỷ giá quy đổi được áp dụng cho giao dịch {{{amount_rate}}}|Những lệnh chuyển tiền tại số tiền {{{amount_rate}}}|Những giao dịch với số tiền {{{amount_rate}}}|Lọc các history của số tiền {{{amount_rate}}}|Các history theo tỷ giá quy đổi được áp dụng cho giao dịch {{{amount_rate}}}|Lọc các lệnh chuyển tiền theo nếu chuyển đổi tiền tệ {{{amount_rate}}}|Lọc các biến động số dư của số tiền {{{amount_rate}}}|Các lệnh chuyển tiền tại hạn mức {{{amount_rate}}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng hold của các giao dịch có trans_type là {{trans_type}}|Xem tổng hold theo trans_type {{trans_type}}|Tính tổng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng hold của các giao dịch có trans_type là {{trans_type}}|Xem tổng hold theo trans_type {{trans_type}}|Tổng cộng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê hold của các giao dịch có trans_type là {{trans_type}}|Xem tổng hold theo trans_type {{trans_type}}|Thống kê số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng hold của các giao dịch có trans_type là {{trans_type}}|Xem tổng hold theo trans_type {{trans_type}}|Cộng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng hold của các giao dịch có trans_type là {{trans_type}}|Xem tổng hold theo trans_type {{trans_type}}|Xem tổng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết history có số tiền {{{block_amount_ref_no}}}|Liệt kê lệnh chuyển tiền với số tiền {{{block_amount_ref_no}}}|Hiển thị history có giá trị {{{block_amount_ref_no}}}|Hiển thị history với mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}|Tìm biến động số dư có mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}|Hiển thị lệnh chuyển tiền có mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}|Liệt kê biến động số dư tại giá trị {{{block_amount_ref_no}}}|Tìm history tại mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}|Liệt kê lệnh chuyển tiền của hạn mức {{{block_amount_ref_no}}}|Kiểm tra lệnh chuyển tiền có giá trị {{{block_amount_ref_no}}}|Cho tôi xem history của giá trị {{{block_amount_ref_no}}}|Tìm lệnh chuyển tiền với hạn mức {{{block_amount_ref_no}}}|Kiểm tra history theo mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}|Liệt kê giao dịch tại hạn mức {{{block_amount_ref_no}}}|Search giao dịch với mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}</t>
-  </si>
-  <si>
-    <t>Tính tổng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}|Tính tổng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}|Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}|Tính tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Tổng cộng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}|Tổng cộng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}|Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}|Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Thống kê đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}|Thống kê người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}|Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}|Thống kê phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Cộng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}|Cộng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}|Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}|Cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Xem tổng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}|Xem tổng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}|Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}|Xem tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}|Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}|Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}|Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}|Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}|Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}|Tính tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Tổng cộng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}|Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Thống kê loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}|Thống kê phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Cộng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}|Cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Xem tổng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}|Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}|Xem tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Tính tổng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Tổng cộng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Thống kê tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Cộng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng phí theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tiền phí theo trans_type {{trans_type}}|Xem tổng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}|Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Cho tôi xem history với tiền phí {{{fee_ind}}}|Tra cứu lệnh chuyển tiền có phí {{{fee_ind}}}|Tra cứu lệnh chuyển tiền tại chỉ số hoặc mã loại phí. {{{fee_ind}}}|Cho tôi xem history theo phí {{{fee_ind}}}|Liệt kê lệnh chuyển tiền của phí {{{fee_ind}}}|Cho tôi xem biến động số dư với chỉ số hoặc mã loại phí. {{{fee_ind}}}|Liệt kê history theo chỉ số hoặc mã loại phí. {{{fee_ind}}}|Liệt kê giao dịch có phí {{{fee_ind}}}|Liệt kê lệnh chuyển tiền có chỉ số hoặc mã loại phí. {{{fee_ind}}}|Tìm biến động số dư theo phí {{{fee_ind}}}|Liệt kê giao dịch với chỉ số hoặc mã loại phí. {{{fee_ind}}}|Search biến động số dư tại phí {{{fee_ind}}}|Xem chi tiết giao dịch theo tiền phí {{{fee_ind}}}|Cho tôi xem lệnh chuyển tiền tại chỉ số hoặc mã loại phí. {{{fee_ind}}}|Hiển thị history theo phí {{{fee_ind}}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu có theo trans_type {{trans_type}}|Tính tổng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu có theo trans_type {{trans_type}}|Tổng cộng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu có theo trans_type {{trans_type}}|Thống kê số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu có theo trans_type {{trans_type}}|Cộng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng nếu có của các giao dịch có trans_type là {{trans_type}}|Xem tổng nếu có theo trans_type {{trans_type}}|Xem tổng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Danh sách giao dịch với loại tiền tệ hoa hồng. {{{commission_currency}}}|Danh sách history tại loại tiền tệ hoa hồng. {{{commission_currency}}}|Những history theo loại tiền tệ hoa hồng. {{{commission_currency}}}|Các biến động số dư mang loại tiền tệ hoa hồng. {{{commission_currency}}}|Các lệnh chuyển tiền của loại tiền tệ hoa hồng. {{{commission_currency}}}|Danh sách giao dịch mang loại tiền tệ hoa hồng. {{{commission_currency}}}|Lọc các history có loại tiền tệ hoa hồng. {{{commission_currency}}}|Những lệnh chuyển tiền với loại tiền tệ hoa hồng. {{{commission_currency}}}|Danh sách lệnh chuyển tiền theo loại tiền tệ hoa hồng. {{{commission_currency}}}|Những history tại loại tiền tệ hoa hồng. {{{commission_currency}}}|Những lệnh chuyển tiền mang loại tiền tệ hoa hồng. {{{commission_currency}}}|Các lệnh chuyển tiền có loại tiền tệ hoa hồng. {{{commission_currency}}}|Danh sách biến động số dư với loại tiền tệ hoa hồng. {{{commission_currency}}}|Lọc các history theo loại tiền tệ hoa hồng. {{{commission_currency}}}|Những giao dịch theo loại tiền tệ hoa hồng. {{{commission_currency}}}</t>
-  </si>
-  <si>
-    <t>Tra cứu lệnh chuyển tiền với chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Kiểm tra lệnh chuyển tiền của chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Xem chi tiết lệnh chuyển tiền của chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Cho tôi xem giao dịch tại chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Search lệnh chuyển tiền mang chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Tra cứu biến động số dư có chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Cho tôi xem history với chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Tìm lệnh chuyển tiền tại chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Cho tôi xem giao dịch với chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Cho tôi xem giao dịch theo chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Xem chi tiết giao dịch theo chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Tìm giao dịch của chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Liệt kê lệnh chuyển tiền tại chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Kiểm tra giao dịch với chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}|Xem chi tiết giao dịch mang chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết history có số tiền {{{promotion_amount}}}|Tra cứu giao dịch có số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}|Liệt kê lệnh chuyển tiền với số tiền {{{promotion_amount}}}|Hiển thị history có giá trị {{{promotion_amount}}}|Search giao dịch tại số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}|Tìm lệnh chuyển tiền theo số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}|Liệt kê biến động số dư tại giá trị {{{promotion_amount}}}|Liệt kê lệnh chuyển tiền tại số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}|Liệt kê lệnh chuyển tiền của hạn mức {{{promotion_amount}}}|Tìm giao dịch có số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}|Kiểm tra lệnh chuyển tiền có giá trị {{{promotion_amount}}}|Cho tôi xem history của giá trị {{{promotion_amount}}}|Tìm lệnh chuyển tiền với hạn mức {{{promotion_amount}}}|Liệt kê giao dịch tại hạn mức {{{promotion_amount}}}|Hiển thị giao dịch tại số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}</t>
-  </si>
-  <si>
-    <t>Hiển thị history với loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Tra cứu biến động số dư mang loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Search biến động số dư mang loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Tra cứu lệnh chuyển tiền của loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Liệt kê giao dịch với loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Kiểm tra lệnh chuyển tiền với loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Tìm biến động số dư theo loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Hiển thị history mang loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Kiểm tra history với loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Hiển thị lệnh chuyển tiền với loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Cho tôi xem giao dịch có loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Search biến động số dư theo loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Search giao dịch có loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Xem chi tiết lệnh chuyển tiền tại loại tiền tệ khuyến mãi. {{{promotion_currency}}}|Hiển thị giao dịch có loại tiền tệ khuyến mãi. {{{promotion_currency}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền mang tỷ lệ khuyến mãi. {{{promotion_rate}}}|Hiển thị giao dịch có tỷ lệ khuyến mãi. {{{promotion_rate}}}|Hiển thị history theo tỷ lệ khuyến mãi. {{{promotion_rate}}}|Kiểm tra giao dịch của tỷ lệ khuyến mãi. {{{promotion_rate}}}|Cho tôi xem biến động số dư mang tỷ lệ khuyến mãi. {{{promotion_rate}}}|Xem chi tiết history có tỷ lệ khuyến mãi. {{{promotion_rate}}}|Xem chi tiết history theo tỷ lệ khuyến mãi. {{{promotion_rate}}}|Xem chi tiết lệnh chuyển tiền theo tỷ lệ khuyến mãi. {{{promotion_rate}}}|Kiểm tra lệnh chuyển tiền tại tỷ lệ khuyến mãi. {{{promotion_rate}}}|Hiển thị biến động số dư có tỷ lệ khuyến mãi. {{{promotion_rate}}}|Liệt kê biến động số dư của tỷ lệ khuyến mãi. {{{promotion_rate}}}|Xem chi tiết lệnh chuyển tiền của tỷ lệ khuyến mãi. {{{promotion_rate}}}|Liệt kê biến động số dư có tỷ lệ khuyến mãi. {{{promotion_rate}}}|Tra cứu giao dịch có tỷ lệ khuyến mãi. {{{promotion_rate}}}|Search history tại tỷ lệ khuyến mãi. {{{promotion_rate}}}</t>
-  </si>
-  <si>
-    <t>Search history tại chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Cho tôi xem giao dịch theo chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Hiển thị giao dịch mang chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Search giao dịch có chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Search lệnh chuyển tiền của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Liệt kê giao dịch có chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Kiểm tra history của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Tìm lệnh chuyển tiền theo chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Kiểm tra giao dịch theo chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Kiểm tra giao dịch mang chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Search lệnh chuyển tiền tại chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Xem chi tiết history mang chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Tìm biến động số dư của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Search biến động số dư tại chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}|Xem chi tiết history theo chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}</t>
-  </si>
-  <si>
-    <t>Liệt kê history có reference number {{{trans_ref_no}}}|Kiểm tra history của số tham chiếu giao dịch {{{trans_ref_no}}}|Xem chi tiết giao dịch mang reference number {{{trans_ref_no}}}|Hiển thị lệnh chuyển tiền mang reference number {{{trans_ref_no}}}|Tra cứu lệnh chuyển tiền có số tham chiếu giao dịch {{{trans_ref_no}}}|Cho tôi xem giao dịch với reference number {{{trans_ref_no}}}|Tra cứu biến động số dư mang số tham chiếu giao dịch {{{trans_ref_no}}}|Xem chi tiết lệnh chuyển tiền mang reference number {{{trans_ref_no}}}|Cho tôi xem giao dịch mang số tham chiếu giao dịch {{{trans_ref_no}}}|Kiểm tra biến động số dư của reference number {{{trans_ref_no}}}|Kiểm tra history có reference number {{{trans_ref_no}}}|Xem chi tiết biến động số dư mang reference number {{{trans_ref_no}}}|Tìm lệnh chuyển tiền với reference number {{{trans_ref_no}}}|Xem chi tiết biến động số dư của reference number {{{trans_ref_no}}}|Cho tôi xem giao dịch tại reference number {{{trans_ref_no}}}</t>
-  </si>
-  <si>
-    <t>Các lệnh chuyển tiền theo kênh gửi yêu cầu {{{request_channel}}}|Những biến động số dư theo kênh {{{request_channel}}}|Các history của tương tự channel_receiver {{{request_channel}}}|Những history có kênh gửi yêu cầu {{{request_channel}}}|Các history mang kênh {{{request_channel}}}|Danh sách lệnh chuyển tiền có nguồn {{{request_channel}}}|Các biến động số dư có tương tự channel_receiver {{{request_channel}}}|Các giao dịch có kênh {{{request_channel}}}|Danh sách history mang kênh {{{request_channel}}}|Các lệnh chuyển tiền với kênh {{{request_channel}}}|Các biến động số dư mang nguồn {{{request_channel}}}|Những history của nguồn {{{request_channel}}}|Lọc các lệnh chuyển tiền mang kênh gửi yêu cầu {{{request_channel}}}|Các biến động số dư mang kênh {{{request_channel}}}|Các biến động số dư mang tương tự channel_receiver {{{request_channel}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra history theo nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}|Tra cứu history theo nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}|Hiển thị biến động số dư theo số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}|Xem chi tiết giao dịch của số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}|Cho tôi xem lệnh chuyển tiền mang nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}|Search biến động số dư mang nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}|Tìm history tại số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}|Cho tôi xem lệnh chuyển tiền có nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}|Kiểm tra lệnh chuyển tiền của nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}|Tìm history với số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}|Xem chi tiết history mang nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}|Hiển thị giao dịch mang số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}|Tìm history của số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}|Xem chi tiết history tại số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}|Search lệnh chuyển tiền theo nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}</t>
-  </si>
-  <si>
-    <t>Tìm history theo mã đối tác tích hợp {{{partner_code}}}|Search lệnh chuyển tiền với ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Hiển thị lệnh chuyển tiền có mã đối tác tích hợp {{{partner_code}}}|Liệt kê lệnh chuyển tiền mang mã đối tác tích hợp {{{partner_code}}}|Hiển thị giao dịch có ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Kiểm tra lệnh chuyển tiền có ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Tìm history mang ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Hiển thị lệnh chuyển tiền có ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Xem chi tiết lệnh chuyển tiền với ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Hiển thị lệnh chuyển tiền tại mã đối tác tích hợp {{{partner_code}}}|Tra cứu giao dịch với ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Tìm biến động số dư có ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Tra cứu history với ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Tìm history có ví dụ: vnpay, momo, zalopay {{{partner_code}}}|Tra cứu biến động số dư với mã đối tác tích hợp {{{partner_code}}}</t>
-  </si>
-  <si>
-    <t>Liệt kê biến động số dư theo ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}|Tra cứu giao dịch có mã phản hồi từ {{{response_code}}}|Xem chi tiết biến động số dư của mã phản hồi từ {{{response_code}}}|Kiểm tra lệnh chuyển tiền có ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}|Kiểm tra biến động số dư theo ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}|Tra cứu biến động số dư với mã phản hồi từ {{{response_code}}}|Kiểm tra biến động số dư tại ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}|Cho tôi xem history có mã phản hồi từ {{{response_code}}}|Hiển thị history có mã phản hồi từ {{{response_code}}}|Xem chi tiết history tại ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}|ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}} là bao nhiêu|Tìm biến động số dư theo ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}|Liệt kê giao dịch tại mã phản hồi từ {{{response_code}}}|Xem chi tiết biến động số dư tại ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}|Xem chi tiết giao dịch có ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}</t>
-  </si>
-  <si>
-    <t>Lọc các lệnh chuyển tiền với trạng thái {{{response_status}}}|Danh sách biến động số dư tại ví dụ: s - success, f - fail {{{response_status}}}|Các biến động số dư tại tình trạng {{{response_status}}}|Những giao dịch theo kết quả {{{response_status}}}|Lọc các biến động số dư có trạng thái phản hồi ngắn gọn {{{response_status}}}|Lọc các history mang trạng thái phản hồi ngắn gọn {{{response_status}}}|Các lệnh chuyển tiền theo tình trạng {{{response_status}}}|Những lệnh chuyển tiền mang trạng thái phản hồi ngắn gọn {{{response_status}}}|Những biến động số dư của trạng thái {{{response_status}}}|Danh sách history tại tình trạng {{{response_status}}}|Lọc các giao dịch với ví dụ: s - success, f - fail {{{response_status}}}|Danh sách giao dịch có trạng thái {{{response_status}}}|Danh sách lệnh chuyển tiền của trạng thái phản hồi ngắn gọn {{{response_status}}}|Lọc các giao dịch với trạng thái {{{response_status}}}|Danh sách biến động số dư của kết quả {{{response_status}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết lệnh chuyển tiền với dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Xem chi tiết giao dịch với dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Cho tôi xem lệnh chuyển tiền mang dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Tìm biến động số dư mang dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Kiểm tra giao dịch tại dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Xem chi tiết lệnh chuyển tiền tại dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Cho tôi xem history có mã lỗi kỹ thuật chi tiết {{{error_code}}}|Hiển thị giao dịch tại dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Hiển thị biến động số dư của dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Tìm history có mã lỗi kỹ thuật chi tiết {{{error_code}}}|Tìm history với mã lỗi kỹ thuật chi tiết {{{error_code}}}|Tìm lệnh chuyển tiền với dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}|Kiểm tra biến động số dư của mã lỗi kỹ thuật chi tiết {{{error_code}}}|Search biến động số dư có mã lỗi kỹ thuật chi tiết {{{error_code}}}|Cho tôi xem history mang dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{checker_id}}}|Cho tôi xem giao dịch của id duyệt giao dịch {{{checker_id}}}|Hiển thị lệnh chuyển tiền mang id {{{checker_id}}}|Tìm history của kiểm soát viên {{{checker_id}}}|Search giao dịch của mã {{{checker_id}}}|Tra cứu lệnh chuyển tiền với kiểm soát viên {{{checker_id}}}|Kiểm tra biến động số dư với id {{{checker_id}}}|Hiển thị biến động số dư với id {{{checker_id}}}|Search lệnh chuyển tiền của id duyệt giao dịch {{{checker_id}}}|Tra cứu biến động số dư với id {{{checker_id}}}|Liệt kê lệnh chuyển tiền với số {{{checker_id}}}|Liệt kê history của mã {{{checker_id}}}|Cho tôi xem giao dịch có số {{{checker_id}}}|Kiểm tra biến động số dư tại mã {{{checker_id}}}|id duyệt giao dịch {{{checker_id}}} là bao nhiêu</t>
-  </si>
-  <si>
-    <t>Tra cứu history mang id tạo lệnh giao dịch {{{maker_id}}}|Kiểm tra lệnh chuyển tiền với mã {{{maker_id}}}|Hiển thị lệnh chuyển tiền mang id {{{maker_id}}}|Xem chi tiết lệnh chuyển tiền mang giao dịch viên {{{maker_id}}}|Search giao dịch của mã {{{maker_id}}}|Xem chi tiết lệnh chuyển tiền tại id tạo lệnh giao dịch {{{maker_id}}}|Kiểm tra biến động số dư với id {{{maker_id}}}|Hiển thị biến động số dư với id {{{maker_id}}}|Tra cứu giao dịch với id tạo lệnh giao dịch {{{maker_id}}}|Hiển thị lệnh chuyển tiền của id tạo lệnh giao dịch {{{maker_id}}}|Tra cứu biến động số dư với id {{{maker_id}}}|Liệt kê lệnh chuyển tiền với số {{{maker_id}}}|Liệt kê history của mã {{{maker_id}}}|Cho tôi xem lệnh chuyển tiền theo giao dịch viên {{{maker_id}}}|Tra cứu lệnh chuyển tiền mang giao dịch viên {{{maker_id}}}</t>
-  </si>
-  <si>
-    <t>Lọc các lệnh chuyển tiền với trạng thái {{{approve_status}}}|Lọc các biến động số dư của ví dụ: a - approved, r - rejected, p - pending {{{approve_status}}}|Các biến động số dư tại tình trạng {{{approve_status}}}|Danh sách lệnh chuyển tiền tại ví dụ: a - approved, r - rejected, p - pending {{{approve_status}}}|Những giao dịch theo kết quả {{{approve_status}}}|Những history có ví dụ: a - approved, r - rejected, p - pending {{{approve_status}}}|Các lệnh chuyển tiền theo tình trạng {{{approve_status}}}|Những biến động số dư của trạng thái {{{approve_status}}}|Danh sách history tại tình trạng {{{approve_status}}}|Danh sách giao dịch có trạng thái {{{approve_status}}}|Những history có trạng thái phê duyệt {{{approve_status}}}|Lọc các giao dịch với trạng thái {{{approve_status}}}|Danh sách biến động số dư của kết quả {{{approve_status}}}|Các biến động số dư với tình trạng {{{approve_status}}}|Các biến động số dư có tình trạng {{{approve_status}}}</t>
-  </si>
-  <si>
-    <t>Lọc các lệnh chuyển tiền với trạng thái {{{trans_status}}}|Các biến động số dư tại tình trạng {{{trans_status}}}|Những giao dịch theo kết quả {{{trans_status}}}|Các lệnh chuyển tiền theo tình trạng {{{trans_status}}}|Những biến động số dư của trạng thái {{{trans_status}}}|Danh sách history tại tình trạng {{{trans_status}}}|Danh sách giao dịch có trạng thái {{{trans_status}}}|Lọc các giao dịch với trạng thái {{{trans_status}}}|Danh sách biến động số dư của kết quả {{{trans_status}}}|Các biến động số dư với tình trạng {{{trans_status}}}|Những lệnh chuyển tiền mang trạng thái cuối cùng giao dịch {{{trans_status}}}|Lọc các lệnh chuyển tiền của trạng thái {{{trans_status}}}|Lọc các lệnh chuyển tiền tại tình trạng {{{trans_status}}}|Những lệnh chuyển tiền tại trạng thái cuối cùng giao dịch {{{trans_status}}}|Các biến động số dư có tình trạng {{{trans_status}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền mang số bút toán {{{core_ref_no}}}|Liệt kê giao dịch tại ft id {{{core_ref_no}}}|Xem chi tiết history mang ft id {{{core_ref_no}}}|Kiểm tra history theo ft id {{{core_ref_no}}}|Liệt kê biến động số dư có ft id {{{core_ref_no}}}|ft id {{{core_ref_no}}} là bao nhiêu|Tìm lệnh chuyển tiền theo số bút toán {{{core_ref_no}}}|Tìm lệnh chuyển tiền của số bút toán {{{core_ref_no}}}|Tra cứu biến động số dư với số bút toán {{{core_ref_no}}}|Kiểm tra history của số bút toán {{{core_ref_no}}}|Tra cứu giao dịch mang số bút toán {{{core_ref_no}}}|Tra cứu biến động số dư mang ft id {{{core_ref_no}}}|Tra cứu lệnh chuyển tiền tại số bút toán {{{core_ref_no}}}|Hiển thị giao dịch có ft id {{{core_ref_no}}}|Tìm history tại ft id {{{core_ref_no}}}</t>
-  </si>
-  <si>
-    <t>Xem chi tiết giao dịch với số bút toán đảo core banking {{{core_revert_ref_no}}}|Cho tôi xem biến động số dư có nếu có {{{core_revert_ref_no}}}|Xem chi tiết giao dịch có nếu có {{{core_revert_ref_no}}}|nếu có {{{core_revert_ref_no}}} là bao nhiêu|Tìm biến động số dư theo số bút toán đảo core banking {{{core_revert_ref_no}}}|Xem chi tiết lệnh chuyển tiền theo nếu có {{{core_revert_ref_no}}}|Tra cứu giao dịch theo số bút toán đảo core banking {{{core_revert_ref_no}}}|Liệt kê lệnh chuyển tiền theo nếu có {{{core_revert_ref_no}}}|Tra cứu lệnh chuyển tiền của nếu có {{{core_revert_ref_no}}}|Liệt kê biến động số dư tại nếu có {{{core_revert_ref_no}}}|Tra cứu biến động số dư có số bút toán đảo core banking {{{core_revert_ref_no}}}|Hiển thị biến động số dư theo nếu có {{{core_revert_ref_no}}}|Cho tôi xem history với nếu có {{{core_revert_ref_no}}}|Hiển thị biến động số dư với nếu có {{{core_revert_ref_no}}}|Search history mang số bút toán đảo core banking {{{core_revert_ref_no}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra biến động số dư tại mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Cho tôi xem lệnh chuyển tiền tại mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Hiển thị giao dịch với mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Kiểm tra lệnh chuyển tiền có mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Kiểm tra lệnh chuyển tiền của mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Hiển thị giao dịch tại mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Xem chi tiết lệnh chuyển tiền theo mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Tra cứu biến động số dư của mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Tra cứu biến động số dư có mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Tìm lệnh chuyển tiền mang mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Tra cứu history theo mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Liệt kê biến động số dư theo mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Search biến động số dư với mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Cho tôi xem giao dịch với mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}|Cho tôi xem history với mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}</t>
-  </si>
-  <si>
-    <t>Lọc các lệnh chuyển tiền với trạng thái {{{payment_status}}}|Các biến động số dư tại tình trạng {{{payment_status}}}|Những giao dịch theo kết quả {{{payment_status}}}|Những giao dịch theo trạng thái trả về từ cổng thanh toán. {{{payment_status}}}|Các lệnh chuyển tiền theo tình trạng {{{payment_status}}}|Những biến động số dư của trạng thái {{{payment_status}}}|Danh sách history tại tình trạng {{{payment_status}}}|Danh sách giao dịch có trạng thái {{{payment_status}}}|Lọc các giao dịch với trạng thái {{{payment_status}}}|Danh sách biến động số dư của kết quả {{{payment_status}}}|Các biến động số dư với tình trạng {{{payment_status}}}|Các biến động số dư mang trạng thái trả về từ cổng thanh toán. {{{payment_status}}}|Các biến động số dư có tình trạng {{{payment_status}}}|Lọc các lệnh chuyển tiền của trạng thái {{{payment_status}}}|Lọc các lệnh chuyển tiền tại tình trạng {{{payment_status}}}</t>
-  </si>
-  <si>
-    <t>Search biến động số dư tại ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Search giao dịch của ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Search giao dịch mang ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Xem chi tiết biến động số dư với mã khách hàng trên hóa đơn {{{bill_customer_code}}}|Tìm biến động số dư theo ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Tìm lệnh chuyển tiền tại ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Search history với mã khách hàng trên hóa đơn {{{bill_customer_code}}}|Hiển thị lệnh chuyển tiền với mã khách hàng trên hóa đơn {{{bill_customer_code}}}|Hiển thị lệnh chuyển tiền mang mã khách hàng trên hóa đơn {{{bill_customer_code}}}|Cho tôi xem history mang ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Xem chi tiết giao dịch tại ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Kiểm tra lệnh chuyển tiền của ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}|Search giao dịch với mã khách hàng trên hóa đơn {{{bill_customer_code}}}|Search lệnh chuyển tiền của mã khách hàng trên hóa đơn {{{bill_customer_code}}}|Tìm biến động số dư tại mã khách hàng trên hóa đơn {{{bill_customer_code}}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{bill_id}}}|Search biến động số dư theo mã định danh hóa đơn hệ thống. {{{bill_id}}}|Hiển thị lệnh chuyển tiền mang id {{{bill_id}}}|Xem chi tiết biến động số dư theo mã định danh hóa đơn hệ thống. {{{bill_id}}}|Search giao dịch của mã {{{bill_id}}}|Tìm giao dịch mang mã định danh hóa đơn hệ thống. {{{bill_id}}}|Kiểm tra biến động số dư với id {{{bill_id}}}|Hiển thị biến động số dư với id {{{bill_id}}}|Liệt kê biến động số dư với mã định danh hóa đơn hệ thống. {{{bill_id}}}|Xem chi tiết history với mã định danh hóa đơn hệ thống. {{{bill_id}}}|Tra cứu biến động số dư với id {{{bill_id}}}|Liệt kê lệnh chuyển tiền với số {{{bill_id}}}|Kiểm tra giao dịch theo mã định danh hóa đơn hệ thống. {{{bill_id}}}|Liệt kê history của mã {{{bill_id}}}|Cho tôi xem giao dịch có số {{{bill_id}}}</t>
-  </si>
-  <si>
-    <t>Danh sách lệnh chuyển tiền theo hình thức {{{bill_type}}}|Lọc các giao dịch với điện, nước, internet, truyền hình... {{{bill_type}}}|Danh sách history theo loại hóa đơn {{{bill_type}}}|Danh sách biến động số dư theo loại {{{bill_type}}}|Các lệnh chuyển tiền tại điện, nước, internet, truyền hình... {{{bill_type}}}|Các lệnh chuyển tiền theo hình thức {{{bill_type}}}|Danh sách giao dịch có hình thức {{{bill_type}}}|Lọc các giao dịch có điện, nước, internet, truyền hình... {{{bill_type}}}|Lọc các biến động số dư của điện, nước, internet, truyền hình... {{{bill_type}}}|Danh sách giao dịch tại hình thức {{{bill_type}}}|Các giao dịch với hình thức {{{bill_type}}}|Lọc các biến động số dư với điện, nước, internet, truyền hình... {{{bill_type}}}|Những biến động số dư tại loại {{{bill_type}}}|Các lệnh chuyển tiền theo điện, nước, internet, truyền hình... {{{bill_type}}}|Lọc các history theo loại {{{bill_type}}}</t>
-  </si>
-  <si>
-    <t>Tìm history theo mã tra cứu hóa đơn. {{{bill_code}}}|Hiển thị lệnh chuyển tiền với mã tra cứu hóa đơn. {{{bill_code}}}|Cho tôi xem giao dịch với mã tra cứu hóa đơn. {{{bill_code}}}|Cho tôi xem biến động số dư của mã tra cứu hóa đơn. {{{bill_code}}}|Xem chi tiết giao dịch với mã tra cứu hóa đơn. {{{bill_code}}}|Search biến động số dư có mã tra cứu hóa đơn. {{{bill_code}}}|Search biến động số dư mang mã tra cứu hóa đơn. {{{bill_code}}}|Cho tôi xem history tại mã tra cứu hóa đơn. {{{bill_code}}}|Tìm lệnh chuyển tiền với mã tra cứu hóa đơn. {{{bill_code}}}|Kiểm tra biến động số dư theo mã tra cứu hóa đơn. {{{bill_code}}}|Tra cứu biến động số dư của mã tra cứu hóa đơn. {{{bill_code}}}|Xem chi tiết biến động số dư theo mã tra cứu hóa đơn. {{{bill_code}}}|Tra cứu lệnh chuyển tiền của mã tra cứu hóa đơn. {{{bill_code}}}|Tra cứu biến động số dư theo mã tra cứu hóa đơn. {{{bill_code}}}|Liệt kê biến động số dư của mã tra cứu hóa đơn. {{{bill_code}}}</t>
-  </si>
-  <si>
-    <t>Lọc các history có loại tiền tệ hóa đơn. {{{bill_currency}}}|Danh sách biến động số dư có loại tiền tệ hóa đơn. {{{bill_currency}}}|Các history mang loại tiền tệ hóa đơn. {{{bill_currency}}}|Lọc các giao dịch theo loại tiền tệ hóa đơn. {{{bill_currency}}}|Những biến động số dư có loại tiền tệ hóa đơn. {{{bill_currency}}}|Danh sách biến động số dư mang loại tiền tệ hóa đơn. {{{bill_currency}}}|Các lệnh chuyển tiền của loại tiền tệ hóa đơn. {{{bill_currency}}}|Lọc các lệnh chuyển tiền có loại tiền tệ hóa đơn. {{{bill_currency}}}|Các giao dịch tại loại tiền tệ hóa đơn. {{{bill_currency}}}|Lọc các biến động số dư mang loại tiền tệ hóa đơn. {{{bill_currency}}}|Các giao dịch của loại tiền tệ hóa đơn. {{{bill_currency}}}|Các lệnh chuyển tiền tại loại tiền tệ hóa đơn. {{{bill_currency}}}|Danh sách giao dịch với loại tiền tệ hóa đơn. {{{bill_currency}}}|Lọc các lệnh chuyển tiền mang loại tiền tệ hóa đơn. {{{bill_currency}}}|Những biến động số dư với loại tiền tệ hóa đơn. {{{bill_currency}}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}|Tính tổng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}|Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}|Tổng cộng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}|Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}|Thống kê trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}|Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}|Cộng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}|Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}|Xem tổng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}|Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}|Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thuế vat theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thuế vat theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thuế vat theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thuế vat theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}|Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền thuế vat theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tính tổng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Kiểm tra lệnh chuyển tiền với mã {{{server_session_id}}}|Hiển thị lệnh chuyển tiền mang id {{{server_session_id}}}|Xem chi tiết history có mã phiên làm việc phía server {{{server_session_id}}}|Search lệnh chuyển tiền với backend session {{{server_session_id}}}|Search giao dịch của mã {{{server_session_id}}}|Kiểm tra history tại mã phiên làm việc phía server {{{server_session_id}}}|Kiểm tra biến động số dư với id {{{server_session_id}}}|Xem chi tiết history của mã phiên làm việc phía server {{{server_session_id}}}|Hiển thị biến động số dư với id {{{server_session_id}}}|Tra cứu biến động số dư với id {{{server_session_id}}}|Liệt kê lệnh chuyển tiền với số {{{server_session_id}}}|Liệt kê history của mã {{{server_session_id}}}|Hiển thị lệnh chuyển tiền tại mã phiên làm việc phía server {{{server_session_id}}}|Cho tôi xem giao dịch có số {{{server_session_id}}}|Kiểm tra biến động số dư tại mã {{{server_session_id}}}</t>
-  </si>
-  <si>
-    <t>Danh sách lệnh chuyển tiền theo hình thức {{{source_type}}}|Danh sách giao dịch của loại nguồn tiền {{{source_type}}}|Danh sách biến động số dư theo loại {{{source_type}}}|Những history tại loại nguồn tiền {{{source_type}}}|Các giao dịch của ví dụ: account - tài khoản thanh toán, card - thẻ, ewallet - ví {{{source_type}}}|Các lệnh chuyển tiền theo hình thức {{{source_type}}}|Danh sách giao dịch có hình thức {{{source_type}}}|Các biến động số dư theo loại nguồn tiền {{{source_type}}}|Những giao dịch theo loại nguồn tiền {{{source_type}}}|Danh sách giao dịch tại hình thức {{{source_type}}}|Các giao dịch với hình thức {{{source_type}}}|Các biến động số dư với ví dụ: account - tài khoản thanh toán, card - thẻ, ewallet - ví {{{source_type}}}|Lọc các biến động số dư mang ví dụ: account - tài khoản thanh toán, card - thẻ, ewallet - ví {{{source_type}}}|Những biến động số dư tại loại {{{source_type}}}|Lọc các history theo loại {{{source_type}}}</t>
-  </si>
-  <si>
-    <t>Cho tôi xem lệnh chuyển tiền với thường được mã hóa hoặc che bớt số {{{card_number}}}|Tra cứu lệnh chuyển tiền của số thẻ {{{card_number}}}|Kiểm tra lệnh chuyển tiền mang số thẻ {{{card_number}}}|Tra cứu biến động số dư có thường được mã hóa hoặc che bớt số {{{card_number}}}|Cho tôi xem lệnh chuyển tiền có số thẻ {{{card_number}}}|Liệt kê lệnh chuyển tiền tại số thẻ {{{card_number}}}|số thẻ {{{card_number}}} là bao nhiêu|Cho tôi xem biến động số dư với thường được mã hóa hoặc che bớt số {{{card_number}}}|Search history của thường được mã hóa hoặc che bớt số {{{card_number}}}|Hiển thị lệnh chuyển tiền theo thường được mã hóa hoặc che bớt số {{{card_number}}}|Cho tôi xem giao dịch có số thẻ {{{card_number}}}|Search giao dịch tại thường được mã hóa hoặc che bớt số {{{card_number}}}|Xem chi tiết history theo số thẻ {{{card_number}}}|Liệt kê giao dịch có số thẻ {{{card_number}}}|Search biến động số dư mang thường được mã hóa hoặc che bớt số {{{card_number}}}</t>
-  </si>
-  <si>
-    <t>Tra cứu history theo mã khách hàng tác nghiệp số {{{cust_no_do}}}|Tìm history mang digital operation {{{cust_no_do}}}|Hiển thị history tại digital operation {{{cust_no_do}}}|Cho tôi xem history theo mã khách hàng tác nghiệp số {{{cust_no_do}}}|Tra cứu history của digital operation {{{cust_no_do}}}|Search history theo mã khách hàng tác nghiệp số {{{cust_no_do}}}|Kiểm tra lệnh chuyển tiền tại digital operation {{{cust_no_do}}}|Search biến động số dư của mã khách hàng tác nghiệp số {{{cust_no_do}}}|Search history của digital operation {{{cust_no_do}}}|Tra cứu history có digital operation {{{cust_no_do}}}|Liệt kê history tại mã khách hàng tác nghiệp số {{{cust_no_do}}}|Cho tôi xem history với digital operation {{{cust_no_do}}}|Tìm giao dịch của mã khách hàng tác nghiệp số {{{cust_no_do}}}|Search lệnh chuyển tiền với mã khách hàng tác nghiệp số {{{cust_no_do}}}|Xem chi tiết biến động số dư tại mã khách hàng tác nghiệp số {{{cust_no_do}}}</t>
-  </si>
-  <si>
-    <t>Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tính tổng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}|Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Tổng cộng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}|Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Thống kê giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}|Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Cộng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Cộng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}|Cộng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}|Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}|Xem tổng số tiền theo trans_type {{trans_type}}|Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}|Xem tổng hạn mức theo trans_type {{trans_type}}|Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}|Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}|Xem tổng giá trị theo trans_type {{trans_type}}</t>
-  </si>
-  <si>
-    <t>Tra cứu biến động số dư có dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Tra cứu giao dịch mang mã danh mục giao dịch {{{category_code}}}|Liệt kê history với dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Search biến động số dư có mã danh mục giao dịch {{{category_code}}}|Liệt kê giao dịch tại mã danh mục giao dịch {{{category_code}}}|Tra cứu biến động số dư tại dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Tra cứu history theo mã danh mục giao dịch {{{category_code}}}|Tra cứu giao dịch theo mã danh mục giao dịch {{{category_code}}}|Hiển thị giao dịch tại mã danh mục giao dịch {{{category_code}}}|Tìm lệnh chuyển tiền tại dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Xem chi tiết giao dịch tại dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Hiển thị giao dịch của dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Liệt kê giao dịch của dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Search lệnh chuyển tiền mang dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}|Tìm biến động số dư theo dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}</t>
-  </si>
-  <si>
-    <t>Liệt kê history có mã cif {{{from_cif_no}}}|Hiển thị biến động số dư với tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}|Search giao dịch của tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}|Xem chi tiết lệnh chuyển tiền tại mã cif {{{from_cif_no}}}|Kiểm tra biến động số dư tại customer information file {{{from_cif_no}}}|Kiểm tra biến động số dư mang tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}|Hiển thị giao dịch với customer information file {{{from_cif_no}}}|Kiểm tra biến động số dư của tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}|Liệt kê history của mã cif {{{from_cif_no}}}|Xem chi tiết history với tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}|Kiểm tra biến động số dư có mã cif {{{from_cif_no}}}|Cho tôi xem giao dịch tại customer information file {{{from_cif_no}}}|Liệt kê giao dịch có tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}|Liệt kê giao dịch tại tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}|Kiểm tra biến động số dư của mã cif {{{from_cif_no}}}</t>
+    <t>Xem chi tiết biến động số dư tại số {{{reference_id}}}
+Cho tôi xem lệnh chuyển tiền mang khóa chính {{{reference_id}}}
+Tra cứu giao dịch tại mã {{{reference_id}}}
+Kiểm tra biến động số dư có mã {{{reference_id}}}
+Search biến động số dư theo primary key {{{reference_id}}}
+Tra cứu giao dịch của số {{{reference_id}}}
+Cho tôi xem giao dịch với id {{{reference_id}}}
+Tra cứu biến động số dư theo số {{{reference_id}}}
+Hiển thị giao dịch mang id {{{reference_id}}}
+Tra cứu giao dịch tại số {{{reference_id}}}
+Hiển thị lệnh chuyển tiền với khóa chính {{{reference_id}}}
+Tìm biến động số dư với số {{{reference_id}}}
+Tra cứu history tại khóa chính {{{reference_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{reference_id}}}
+mã {{{reference_id}}} là bao nhiêu</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{trans_id}}}
+Kiểm tra giao dịch của có thể tra soát {{{trans_id}}}
+Tra cứu giao dịch tại mã {{{trans_id}}}
+Kiểm tra biến động số dư có mã {{{trans_id}}}
+Search history với mã định danh giao dịch theo nghiệp vụ, phân biệt các giao dịch với nhau {{{trans_id}}}
+Tra cứu giao dịch của số {{{trans_id}}}
+Cho tôi xem giao dịch với id {{{trans_id}}}
+Kiểm tra biến động số dư theo có thể tra soát {{{trans_id}}}
+Tra cứu biến động số dư theo số {{{trans_id}}}
+Tìm history của có thể tra soát {{{trans_id}}}
+Hiển thị lệnh chuyển tiền của mã định danh giao dịch theo nghiệp vụ, phân biệt các giao dịch với nhau {{{trans_id}}}
+Tra cứu giao dịch tại số {{{trans_id}}}
+Tìm history có có thể tra soát {{{trans_id}}}
+Tìm lệnh chuyển tiền tại mã định danh giao dịch theo nghiệp vụ, phân biệt các giao dịch với nhau {{{trans_id}}}
+Hiển thị giao dịch mang id {{{trans_id}}}</t>
+  </si>
+  <si>
+    <t>Kiểm tra biến động số dư với mã loại hình giao dịch {{{trans_code}}}
+Tra cứu biến động số dư tại mã loại hình giao dịch {{{trans_code}}}
+Kiểm tra lệnh chuyển tiền với ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Hiển thị biến động số dư mang mã loại hình giao dịch {{{trans_code}}}
+Cho tôi xem lệnh chuyển tiền theo ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Cho tôi xem lệnh chuyển tiền tại ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Kiểm tra lệnh chuyển tiền của ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Xem chi tiết history theo ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Xem chi tiết history của ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Xem chi tiết lệnh chuyển tiền có ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Tìm giao dịch tại mã loại hình giao dịch {{{trans_code}}}
+Kiểm tra biến động số dư có ví dụ: ck_noi_bo - chuyển khoản nội bộ, thanh_toan_hoa_don {{{trans_code}}}
+Tra cứu giao dịch theo mã loại hình giao dịch {{{trans_code}}}
+Tìm lệnh chuyển tiền với mã loại hình giao dịch {{{trans_code}}}
+Search biến động số dư của mã loại hình giao dịch {{{trans_code}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{parent_id}}}
+Tra cứu giao dịch tại mã {{{parent_id}}}
+Kiểm tra biến động số dư có mã {{{parent_id}}}
+Tra cứu giao dịch của số {{{parent_id}}}
+Cho tôi xem giao dịch với id {{{parent_id}}}
+Tra cứu biến động số dư theo số {{{parent_id}}}
+Hiển thị giao dịch mang id {{{parent_id}}}
+Tra cứu giao dịch tại số {{{parent_id}}}
+Tìm biến động số dư với số {{{parent_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{parent_id}}}
+Cho tôi xem biến động số dư của id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp. {{{parent_id}}}
+mã {{{parent_id}}} là bao nhiêu
+Tìm giao dịch với id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp. {{{parent_id}}}
+Cho tôi xem giao dịch tại id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp. {{{parent_id}}}
+Search biến động số dư theo mã {{{parent_id}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{node_id}}}
+Tra cứu giao dịch tại mã {{{node_id}}}
+Kiểm tra biến động số dư có mã {{{node_id}}}
+Hiển thị history mang máy chủ hoặc phân vùng dữ liệu {{{node_id}}}
+Tra cứu giao dịch của số {{{node_id}}}
+Cho tôi xem giao dịch với id {{{node_id}}}
+Tra cứu biến động số dư theo số {{{node_id}}}
+Hiển thị giao dịch mang id {{{node_id}}}
+Tra cứu giao dịch tại số {{{node_id}}}
+Search biến động số dư theo mã định danh node {{{node_id}}}
+Tìm biến động số dư với số {{{node_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{node_id}}}
+mã {{{node_id}}} là bao nhiêu
+Search biến động số dư theo mã {{{node_id}}}
+Tra cứu lệnh chuyển tiền tại mã {{{node_id}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{user_id}}}
+Cho tôi xem giao dịch theo người dùng {{{user_id}}}
+Tra cứu giao dịch của số {{{user_id}}}
+Hiển thị giao dịch mang id {{{user_id}}}
+Tìm giao dịch có mã định danh {{{user_id}}}
+Tìm biến động số dư với số {{{user_id}}}
+Cho tôi xem lệnh chuyển tiền tại người dùng {{{user_id}}}
+Kiểm tra lệnh chuyển tiền tại người dùng {{{user_id}}}
+Search biến động số dư theo mã {{{user_id}}}
+Liệt kê lệnh chuyển tiền có thường khóa ngoại trỏ sang bảng user {{{user_id}}}
+Kiểm tra giao dịch tại thường khóa ngoại trỏ sang bảng user {{{user_id}}}
+Liệt kê lệnh chuyển tiền tại số {{{user_id}}}
+Tìm history tại id {{{user_id}}}
+Xem chi tiết history với mã {{{user_id}}}
+Liệt kê giao dịch theo mã định danh {{{user_id}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị lệnh chuyển tiền với web/app session {{{session_id}}}
+Xem chi tiết biến động số dư tại số {{{session_id}}}
+Tra cứu giao dịch tại mã {{{session_id}}}
+Hiển thị biến động số dư với web/app session {{{session_id}}}
+Kiểm tra biến động số dư có mã {{{session_id}}}
+Cho tôi xem biến động số dư với web/app session {{{session_id}}}
+Tra cứu giao dịch của số {{{session_id}}}
+Cho tôi xem giao dịch với id {{{session_id}}}
+Tra cứu biến động số dư theo số {{{session_id}}}
+Tìm history của session {{{session_id}}}
+Hiển thị giao dịch mang id {{{session_id}}}
+Tra cứu giao dịch tại số {{{session_id}}}
+Kiểm tra history của session {{{session_id}}}
+mã phiên làm việc {{{session_id}}} là bao nhiêu
+Tìm history theo session {{{session_id}}}</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch từ ngày {{start_date}} đến {{end_date}}
+Liệt kê lịch sử trong khoảng thời gian {{start_date}} - {{end_date}}
+Kiểm tra giao dịch phát sinh từ {{start_date}} tới {{end_date}}
+Cho tôi xem biến động số dư giữa {{start_date}} và {{end_date}}</t>
+  </si>
+  <si>
+    <t>Các giao dịch của hình thức {{{trans_type}}}
+Các biến động số dư mang loại giao dịch chi tiết hoặc mô tả nhóm giao dịch. {{{trans_type}}}
+Danh sách biến động số dư theo loại giao dịch chi tiết hoặc mô tả nhóm giao dịch. {{{trans_type}}}
+Danh sách giao dịch với loại {{{trans_type}}}
+Lọc các giao dịch tại loại giao dịch chi tiết hoặc mô tả nhóm giao dịch. {{{trans_type}}}
+Danh sách biến động số dư tại loại giao dịch chi tiết hoặc mô tả nhóm giao dịch. {{{trans_type}}}
+Các giao dịch với loại {{{trans_type}}}
+Các lệnh chuyển tiền theo hình thức {{{trans_type}}}
+Các lệnh chuyển tiền tại hình thức {{{trans_type}}}
+Các history với loại {{{trans_type}}}
+Lọc các giao dịch theo hình thức {{{trans_type}}}
+Các giao dịch mang loại {{{trans_type}}}
+Các history có loại {{{trans_type}}}
+Các giao dịch tại hình thức {{{trans_type}}}
+Danh sách biến động số dư theo loại {{{trans_type}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị lệnh chuyển tiền mang mã hành động cụ thể mà thực hiện {{{action_id}}}
+Xem chi tiết biến động số dư tại số {{{action_id}}}
+Tra cứu giao dịch tại mã {{{action_id}}}
+Kiểm tra biến động số dư có mã {{{action_id}}}
+Tra cứu giao dịch của số {{{action_id}}}
+Cho tôi xem giao dịch với id {{{action_id}}}
+Tra cứu biến động số dư theo số {{{action_id}}}
+Hiển thị giao dịch mang id {{{action_id}}}
+Tra cứu giao dịch tại số {{{action_id}}}
+Search history của ví dụ: nút bấm "xác nhận", "gửi otp" {{{action_id}}}
+Hiển thị giao dịch theo mã hành động cụ thể mà thực hiện {{{action_id}}}
+Tìm biến động số dư với số {{{action_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{action_id}}}
+mã {{{action_id}}} là bao nhiêu
+Search biến động số dư theo mã {{{action_id}}}</t>
+  </si>
+  <si>
+    <t>Những lệnh chuyển tiền tại kênh tiếp nhận giao dịch {{{channel_receiver}}}
+Danh sách biến động số dư theo kênh tiếp nhận giao dịch {{{channel_receiver}}}
+Danh sách biến động số dư mang ví dụ: mobile app, internet banking, atm, counter {{{channel_receiver}}}
+Lọc các history của kênh tiếp nhận giao dịch {{{channel_receiver}}}
+Lọc các giao dịch của kênh {{{channel_receiver}}}
+Danh sách history tại ví dụ: mobile app, internet banking, atm, counter {{{channel_receiver}}}
+Những history theo nguồn {{{channel_receiver}}}
+Các history có nguồn {{{channel_receiver}}}
+Lọc các giao dịch theo nguồn {{{channel_receiver}}}
+Danh sách lệnh chuyển tiền mang kênh tiếp nhận giao dịch {{{channel_receiver}}}
+Danh sách giao dịch với ví dụ: mobile app, internet banking, atm, counter {{{channel_receiver}}}
+Những lệnh chuyển tiền của kênh tiếp nhận giao dịch {{{channel_receiver}}}
+Lọc các history tại nguồn {{{channel_receiver}}}
+Lọc các history của nguồn {{{channel_receiver}}}
+Danh sách history của ví dụ: mobile app, internet banking, atm, counter {{{channel_receiver}}}</t>
+  </si>
+  <si>
+    <t>Các giao dịch của hình thức {{{stak_user_type_do}}}
+Các lệnh chuyển tiền theo hình thức {{{stak_user_type_do}}}
+Các lệnh chuyển tiền tại hình thức {{{stak_user_type_do}}}
+Lọc các history của khách hàng {{{stak_user_type_do}}}
+Các giao dịch mang loại {{{stak_user_type_do}}}
+Danh sách giao dịch của loại tác nghiệp {{{stak_user_type_do}}}
+Lọc các history theo thường cho nhân viên vận hành/digital officer {{{stak_user_type_do}}}
+Danh sách biến động số dư mang loại tác nghiệp {{{stak_user_type_do}}}
+Lọc các history tại người dùng {{{stak_user_type_do}}}
+Các giao dịch tại loại {{{stak_user_type_do}}}
+Những giao dịch mang loại {{{stak_user_type_do}}}
+Lọc các biến động số dư của loại {{{stak_user_type_do}}}
+Lọc các giao dịch theo người dùng {{{stak_user_type_do}}}
+Những history mang loại tác nghiệp {{{stak_user_type_do}}}
+Lọc các giao dịch theo loại tác nghiệp {{{stak_user_type_do}}}</t>
+  </si>
+  <si>
+    <t>Kiểm tra giao dịch mang tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này {{{user_do}}}
+Tìm biến động số dư tại tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này {{{user_do}}}
+Cho tôi xem giao dịch theo người dùng {{{user_do}}}
+Kiểm tra giao dịch với khách hàng {{{user_do}}}
+Kiểm tra biến động số dư mang nếu có {{{user_do}}}
+Tìm lệnh chuyển tiền với khách hàng {{{user_do}}}
+Liệt kê history của người dùng {{{user_do}}}
+Cho tôi xem lệnh chuyển tiền tại người dùng {{{user_do}}}
+Cho tôi xem history của tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này {{{user_do}}}
+Kiểm tra lệnh chuyển tiền tại người dùng {{{user_do}}}
+Tra cứu history với tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này {{{user_do}}}
+Cho tôi xem history của người dùng {{{user_do}}}
+Search giao dịch mang người dùng {{{user_do}}}
+Hiển thị giao dịch với người dùng {{{user_do}}}
+Hiển thị biến động số dư mang khách hàng {{{user_do}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu biến động số dư tại digital office branch {{{branch_code_do}}}
+Tìm lệnh chuyển tiền theo mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}
+Liệt kê giao dịch của mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}
+Search biến động số dư với mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}
+Kiểm tra history có digital office branch {{{branch_code_do}}}
+Kiểm tra giao dịch theo digital office branch {{{branch_code_do}}}
+Hiển thị biến động số dư mang digital office branch {{{branch_code_do}}}
+Kiểm tra biến động số dư tại digital office branch {{{branch_code_do}}}
+Search biến động số dư tại mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}
+Hiển thị biến động số dư với digital office branch {{{branch_code_do}}}
+Cho tôi xem history mang mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}
+Liệt kê lệnh chuyển tiền theo digital office branch {{{branch_code_do}}}
+Xem chi tiết biến động số dư tại mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}
+Search biến động số dư theo mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}
+Search lệnh chuyển tiền theo mã chi nhánh nhân viên vận hành/hỗ trợ {{{branch_code_do}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{product_id}}}
+Tra cứu giao dịch tại mã {{{product_id}}}
+Search history của ví dụ: gói tài khoản, gói vay {{{product_id}}}
+Kiểm tra biến động số dư có mã {{{product_id}}}
+Tra cứu giao dịch của số {{{product_id}}}
+Cho tôi xem giao dịch với id {{{product_id}}}
+Tra cứu biến động số dư theo số {{{product_id}}}
+Tìm biến động số dư với ví dụ: gói tài khoản, gói vay {{{product_id}}}
+Hiển thị giao dịch mang id {{{product_id}}}
+Tra cứu giao dịch có ví dụ: gói tài khoản, gói vay {{{product_id}}}
+Tra cứu giao dịch tại số {{{product_id}}}
+Liệt kê biến động số dư mang mã sản phẩm hoặc dịch vụ liên quan đến giao dịch {{{product_id}}}
+Xem chi tiết lệnh chuyển tiền của mã sản phẩm hoặc dịch vụ liên quan đến giao dịch {{{product_id}}}
+Tìm biến động số dư với số {{{product_id}}}
+Liệt kê giao dịch tại mã sản phẩm hoặc dịch vụ liên quan đến giao dịch {{{product_id}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu lệnh chuyển tiền mang app/web {{{request_id}}}
+Xem chi tiết biến động số dư tại số {{{request_id}}}
+Tra cứu giao dịch tại mã {{{request_id}}}
+Kiểm tra biến động số dư có mã {{{request_id}}}
+Tra cứu giao dịch của số {{{request_id}}}
+Cho tôi xem giao dịch với id {{{request_id}}}
+Tra cứu biến động số dư theo số {{{request_id}}}
+Hiển thị giao dịch mang id {{{request_id}}}
+mã yêu cầu duy nhất được sinh ra từ phía client {{{request_id}}} là bao nhiêu
+Tra cứu giao dịch tại số {{{request_id}}}
+Tra cứu history mang app/web {{{request_id}}}
+Liệt kê history với mã yêu cầu duy nhất được sinh ra từ phía client {{{request_id}}}
+Tìm biến động số dư với số {{{request_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{request_id}}}
+mã {{{request_id}}} là bao nhiêu</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{original_request_id}}}
+Tra cứu giao dịch tại mã {{{original_request_id}}}
+Kiểm tra biến động số dư có mã {{{original_request_id}}}
+Tra cứu giao dịch của số {{{original_request_id}}}
+Cho tôi xem giao dịch với id {{{original_request_id}}}
+Tra cứu biến động số dư theo số {{{original_request_id}}}
+Tra cứu history tại dùng cho các giao dịch hoàn tiền, hủy hoặc đảo giao dịch tham chiếu lại giao dịch cũ {{{original_request_id}}}
+Hiển thị giao dịch mang id {{{original_request_id}}}
+Tra cứu giao dịch tại số {{{original_request_id}}}
+Search history với mã yêu cầu gốc {{{original_request_id}}}
+Hiển thị giao dịch mang dùng cho các giao dịch hoàn tiền, hủy hoặc đảo giao dịch tham chiếu lại giao dịch cũ {{{original_request_id}}}
+Tìm biến động số dư với số {{{original_request_id}}}
+Xem chi tiết lệnh chuyển tiền tại mã yêu cầu gốc {{{original_request_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{original_request_id}}}
+Tìm history theo mã yêu cầu gốc {{{original_request_id}}}</t>
+  </si>
+  <si>
+    <t>Tìm history theo hình thức {{{input_type}}}
+Cho tôi xem lệnh chuyển tiền mang loại {{{input_type}}}
+Cho tôi xem lệnh chuyển tiền mang hình thức {{{input_type}}}
+Tra cứu giao dịch tại loại dữ liệu đầu vào {{{input_type}}}
+Kiểm tra history của ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}
+Liệt kê biến động số dư có hình thức {{{input_type}}}
+Cho tôi xem history mang ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}
+Tra cứu biến động số dư theo loại dữ liệu đầu vào {{{input_type}}}
+Tìm giao dịch của loại dữ liệu đầu vào {{{input_type}}}
+Liệt kê biến động số dư mang loại {{{input_type}}}
+Xem chi tiết giao dịch với hình thức {{{input_type}}}
+Tìm lệnh chuyển tiền với hình thức {{{input_type}}}
+Liệt kê giao dịch mang ví dụ: manual - nhập tay, qrcode - quét mã, contact - chọn từ danh bạ {{{input_type}}}
+Kiểm tra lệnh chuyển tiền có loại {{{input_type}}}
+Tìm giao dịch với loại dữ liệu đầu vào {{{input_type}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu giao dịch của ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Kiểm tra giao dịch mang ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Search history với ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Kiểm tra lệnh chuyển tiền của ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Hiển thị history mang giá trị đầu vào tương ứng {{{input_value}}}
+Tra cứu history với giá trị đầu vào tương ứng {{{input_value}}}
+Cho tôi xem lệnh chuyển tiền của ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Xem chi tiết giao dịch theo giá trị đầu vào tương ứng {{{input_value}}}
+Kiểm tra lệnh chuyển tiền tại ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Xem chi tiết history mang ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Hiển thị lệnh chuyển tiền tại ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Tìm history mang ví dụ: chuỗi mã qr, số điện thoại được chọn {{{input_value}}}
+Tra cứu biến động số dư với giá trị đầu vào tương ứng {{{input_value}}}
+Kiểm tra giao dịch với giá trị đầu vào tương ứng {{{input_value}}}
+Tìm biến động số dư theo giá trị đầu vào tương ứng {{{input_value}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{from_system_id}}}
+Liệt kê giao dịch có mã nguồn khởi tạo giao dịch {{{from_system_id}}}
+Tra cứu giao dịch tại mã {{{from_system_id}}}
+Liệt kê lệnh chuyển tiền với mã nguồn khởi tạo giao dịch {{{from_system_id}}}
+Kiểm tra biến động số dư có mã {{{from_system_id}}}
+Search history tại mã nguồn khởi tạo giao dịch {{{from_system_id}}}
+Tra cứu giao dịch của số {{{from_system_id}}}
+Cho tôi xem giao dịch với id {{{from_system_id}}}
+Tra cứu biến động số dư theo số {{{from_system_id}}}
+Hiển thị giao dịch mang id {{{from_system_id}}}
+Tra cứu giao dịch tại số {{{from_system_id}}}
+Liệt kê history của nếu giao dịch đến từ đối tác hoặc vệ tinh {{{from_system_id}}}
+Search giao dịch của mã nguồn khởi tạo giao dịch {{{from_system_id}}}
+Search lệnh chuyển tiền có nếu giao dịch đến từ đối tác hoặc vệ tinh {{{from_system_id}}}
+Cho tôi xem giao dịch của nếu giao dịch đến từ đối tác hoặc vệ tinh {{{from_system_id}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{from_cust_id}}}
+Xem chi tiết history với id khách hàng chuyển tiền/người thanh toán. {{{from_cust_id}}}
+Tra cứu giao dịch tại mã {{{from_cust_id}}}
+Kiểm tra biến động số dư có mã {{{from_cust_id}}}
+Tra cứu giao dịch của số {{{from_cust_id}}}
+Cho tôi xem giao dịch với id {{{from_cust_id}}}
+Tra cứu biến động số dư theo số {{{from_cust_id}}}
+Hiển thị giao dịch mang id {{{from_cust_id}}}
+Tra cứu giao dịch tại số {{{from_cust_id}}}
+Tìm biến động số dư với số {{{from_cust_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{from_cust_id}}}
+Liệt kê history của id khách hàng chuyển tiền/người thanh toán. {{{from_cust_id}}}
+mã {{{from_cust_id}}} là bao nhiêu
+Hiển thị history mang id khách hàng chuyển tiền/người thanh toán. {{{from_cust_id}}}
+Search biến động số dư theo mã {{{from_cust_id}}}</t>
+  </si>
+  <si>
+    <t>Cho tôi xem giao dịch với customer information file {{{from_cust_no}}}
+Cho tôi xem lệnh chuyển tiền với mã cif {{{from_cust_no}}}
+Cho tôi xem giao dịch của customer information file {{{from_cust_no}}}
+Liệt kê giao dịch với mã cif {{{from_cust_no}}}
+Kiểm tra lệnh chuyển tiền với mã cif {{{from_cust_no}}}
+Liệt kê history với mã cif {{{from_cust_no}}}
+Tìm history có customer information file {{{from_cust_no}}}
+Xem chi tiết history với mã cif {{{from_cust_no}}}
+Tìm lệnh chuyển tiền với mã cif {{{from_cust_no}}}
+Tìm biến động số dư với customer information file {{{from_cust_no}}}
+Search lệnh chuyển tiền với mã cif {{{from_cust_no}}}
+Xem chi tiết history với customer information file {{{from_cust_no}}}
+Cho tôi xem lệnh chuyển tiền của mã cif {{{from_cust_no}}}
+Tìm lệnh chuyển tiền mang mã cif {{{from_cust_no}}}
+Tìm giao dịch có customer information file {{{from_cust_no}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu lệnh chuyển tiền tại mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Xem chi tiết history tại mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Xem chi tiết giao dịch của mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Search biến động số dư mang mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Kiểm tra giao dịch của mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Cho tôi xem biến động số dư mang mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Xem chi tiết lệnh chuyển tiền tại mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Search history theo mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Kiểm tra lệnh chuyển tiền của mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Tra cứu lệnh chuyển tiền của mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Xem chi tiết biến động số dư tại mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Kiểm tra biến động số dư có mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+Hiển thị biến động số dư tại mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}
+mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}} là bao nhiêu
+Tra cứu giao dịch của mã chi nhánh quản lý khách hàng chuyển. {{{from_cust_branch}}}</t>
+  </si>
+  <si>
+    <t>Các giao dịch với hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}
+Danh sách biến động số dư theo hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}
+Những giao dịch theo hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}
+Những history tại ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}
+Những giao dịch mang hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}
+Lọc các biến động số dư tại ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}
+Những biến động số dư tại ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}
+Các history mang ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}
+Lọc các lệnh chuyển tiền theo ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}
+Lọc các biến động số dư theo hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}
+Danh sách lệnh chuyển tiền theo hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}
+Những biến động số dư với hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}
+Những biến động số dư mang ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}
+Những lệnh chuyển tiền của ví dụ: dda - thanh toán, fd - tiết kiệm {{{from_account_class}}}
+Danh sách history mang hạng hoặc nhóm tài khoản nguồn {{{from_account_class}}}</t>
+  </si>
+  <si>
+    <t>Những giao dịch với loại tài khoản nguồn chi tiết. {{{from_account_type}}}
+Các history mang loại tài khoản nguồn chi tiết. {{{from_account_type}}}
+Các giao dịch của hình thức {{{from_account_type}}}
+Các biến động số dư tại loại tài khoản nguồn chi tiết. {{{from_account_type}}}
+Những giao dịch mang loại tài khoản nguồn chi tiết. {{{from_account_type}}}
+Danh sách giao dịch với loại {{{from_account_type}}}
+Các lệnh chuyển tiền theo hình thức {{{from_account_type}}}
+Các giao dịch với loại {{{from_account_type}}}
+Các lệnh chuyển tiền tại hình thức {{{from_account_type}}}
+Các history với loại {{{from_account_type}}}
+Những biến động số dư theo loại tài khoản nguồn chi tiết. {{{from_account_type}}}
+Lọc các giao dịch theo hình thức {{{from_account_type}}}
+Các giao dịch mang loại {{{from_account_type}}}
+Lọc các history tại loại tài khoản nguồn chi tiết. {{{from_account_type}}}
+Các lệnh chuyển tiền mang loại tài khoản nguồn chi tiết. {{{from_account_type}}}</t>
+  </si>
+  <si>
+    <t>Tìm lệnh chuyển tiền mang số tài khoản chuyển tiền {{{from_account_no}}}
+Search lệnh chuyển tiền mang số tài khoản chuyển tiền {{{from_account_no}}}
+Tra cứu lệnh chuyển tiền của tài khoản nguồn {{{from_account_no}}}
+Cho tôi xem lệnh chuyển tiền tại số tài khoản chuyển tiền {{{from_account_no}}}
+Cho tôi xem biến động số dư của số tài khoản chuyển tiền {{{from_account_no}}}
+Hiển thị lệnh chuyển tiền của số tài khoản chuyển tiền {{{from_account_no}}}
+Tìm giao dịch tại tài khoản nguồn {{{from_account_no}}}
+Hiển thị lệnh chuyển tiền theo số tài khoản chuyển tiền {{{from_account_no}}}
+Liệt kê giao dịch mang tài khoản nguồn {{{from_account_no}}}
+Search lệnh chuyển tiền theo tài khoản nguồn {{{from_account_no}}}
+Cho tôi xem biến động số dư theo tài khoản nguồn {{{from_account_no}}}
+Liệt kê giao dịch của số tài khoản chuyển tiền {{{from_account_no}}}
+Liệt kê lệnh chuyển tiền với số tài khoản chuyển tiền {{{from_account_no}}}
+Liệt kê giao dịch theo số tài khoản chuyển tiền {{{from_account_no}}}
+Xem chi tiết giao dịch có tài khoản nguồn {{{from_account_no}}}</t>
+  </si>
+  <si>
+    <t>Liệt kê history tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Cho tôi xem lệnh chuyển tiền theo mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Hiển thị history mang mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Tìm giao dịch của mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Hiển thị biến động số dư với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Search history tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Cho tôi xem giao dịch mang mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Kiểm tra lệnh chuyển tiền với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Hiển thị lệnh chuyển tiền của mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Xem chi tiết history tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Xem chi tiết history mang mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Tra cứu biến động số dư với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Liệt kê giao dịch tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Hiển thị lệnh chuyển tiền tại mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}
+Cho tôi xem lệnh chuyển tiền với mã chi nhánh quản lý tài khoản nguồn. {{{from_account_branch}}}</t>
+  </si>
+  <si>
+    <t>Những history có vnd, usd, eur... {{{from_account_currency}}}
+Các history theo loại tiền tệ tài khoản nguồn {{{from_account_currency}}}
+Lọc các giao dịch với vnd, usd, eur... {{{from_account_currency}}}
+Danh sách history của loại tiền tệ tài khoản nguồn {{{from_account_currency}}}
+Các lệnh chuyển tiền theo vnd, usd, eur... {{{from_account_currency}}}
+Những history có loại tiền tệ tài khoản nguồn {{{from_account_currency}}}
+Danh sách history của vnd, usd, eur... {{{from_account_currency}}}
+Những lệnh chuyển tiền với vnd, usd, eur... {{{from_account_currency}}}
+Các lệnh chuyển tiền có vnd, usd, eur... {{{from_account_currency}}}
+Lọc các biến động số dư có vnd, usd, eur... {{{from_account_currency}}}
+Các history của vnd, usd, eur... {{{from_account_currency}}}
+Những history theo vnd, usd, eur... {{{from_account_currency}}}
+Danh sách history tại loại tiền tệ tài khoản nguồn {{{from_account_currency}}}
+Các giao dịch có loại tiền tệ tài khoản nguồn {{{from_account_currency}}}
+Các giao dịch mang vnd, usd, eur... {{{from_account_currency}}}</t>
+  </si>
+  <si>
+    <t>Lọc các biến động số dư của tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Danh sách lệnh chuyển tiền theo tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Những biến động số dư với tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Các biến động số dư có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Các biến động số dư tại tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Các history có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Lọc các lệnh chuyển tiền với tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Những biến động số dư theo tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Lọc các biến động số dư có tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Lọc các lệnh chuyển tiền tại tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Các history theo tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Lọc các history theo tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Các lệnh chuyển tiền theo tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Các history với tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}
+Lọc các giao dịch mang tên đầy đủ chủ tài khoản nguồn. {{{from_account_fullname}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{to_system_id}}}
+Tra cứu giao dịch tại mã {{{to_system_id}}}
+Liệt kê history có mã đích {{{to_system_id}}}
+Kiểm tra biến động số dư có mã {{{to_system_id}}}
+Tra cứu giao dịch của số {{{to_system_id}}}
+Cho tôi xem giao dịch với id {{{to_system_id}}}
+Tra cứu biến động số dư theo số {{{to_system_id}}}
+Cho tôi xem biến động số dư theo nơi nhận tiền/giao dịch {{{to_system_id}}}
+Hiển thị giao dịch mang id {{{to_system_id}}}
+Tra cứu giao dịch tại số {{{to_system_id}}}
+Xem chi tiết history theo nơi nhận tiền/giao dịch {{{to_system_id}}}
+Tìm biến động số dư có mã đích {{{to_system_id}}}
+Hiển thị lệnh chuyển tiền với nơi nhận tiền/giao dịch {{{to_system_id}}}
+Kiểm tra biến động số dư mang mã đích {{{to_system_id}}}
+Tìm biến động số dư với số {{{to_system_id}}}</t>
+  </si>
+  <si>
+    <t>Search history của nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Search biến động số dư mang nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Hiển thị giao dịch có mã khách hàng thụ hưởng {{{to_cust_no}}}
+Xem chi tiết lệnh chuyển tiền mang nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Liệt kê lệnh chuyển tiền với nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Tra cứu history mang mã khách hàng thụ hưởng {{{to_cust_no}}}
+Tra cứu giao dịch của mã khách hàng thụ hưởng {{{to_cust_no}}}
+Liệt kê history với nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Liệt kê giao dịch tại mã khách hàng thụ hưởng {{{to_cust_no}}}
+Tra cứu lệnh chuyển tiền tại mã khách hàng thụ hưởng {{{to_cust_no}}}
+Tìm giao dịch của nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Kiểm tra lệnh chuyển tiền với mã khách hàng thụ hưởng {{{to_cust_no}}}
+Hiển thị lệnh chuyển tiền của nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Xem chi tiết giao dịch theo nếu chuyển khoản nội bộ {{{to_cust_no}}}
+Search giao dịch tại nếu chuyển khoản nội bộ {{{to_cust_no}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu giao dịch của mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Kiểm tra lệnh chuyển tiền theo mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Search lệnh chuyển tiền có mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Tra cứu history của mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Cho tôi xem biến động số dư mang mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Search history của mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Hiển thị giao dịch có mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Tra cứu giao dịch với mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Cho tôi xem lệnh chuyển tiền với mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Cho tôi xem giao dịch với mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Liệt kê giao dịch theo mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Hiển thị giao dịch mang mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Tìm lệnh chuyển tiền theo mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Search giao dịch mang mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}
+Hiển thị giao dịch của mã chi nhánh quản lý khách hàng thụ hưởng. {{{to_cust_branch}}}</t>
+  </si>
+  <si>
+    <t>Tìm lệnh chuyển tiền mang số tài khoản nhận tiền {{{to_account_no}}}
+Tra cứu giao dịch của số tài khoản nhận tiền {{{to_account_no}}}
+Xem chi tiết biến động số dư theo số tài khoản nhận tiền {{{to_account_no}}}
+Tìm lệnh chuyển tiền theo số tài khoản nhận tiền {{{to_account_no}}}
+Hiển thị giao dịch mang tài khoản đích {{{to_account_no}}}
+Tra cứu giao dịch mang số tài khoản nhận tiền {{{to_account_no}}}
+Hiển thị giao dịch với số tài khoản nhận tiền {{{to_account_no}}}
+Liệt kê giao dịch với tài khoản đích {{{to_account_no}}}
+Tra cứu biến động số dư của số tài khoản nhận tiền {{{to_account_no}}}
+Liệt kê lệnh chuyển tiền mang tài khoản đích {{{to_account_no}}}
+Tìm lệnh chuyển tiền của số tài khoản nhận tiền {{{to_account_no}}}
+Tra cứu biến động số dư mang số tài khoản nhận tiền {{{to_account_no}}}
+Hiển thị history theo tài khoản đích {{{to_account_no}}}
+Hiển thị history với số tài khoản nhận tiền {{{to_account_no}}}
+Tìm lệnh chuyển tiền mang tài khoản đích {{{to_account_no}}}</t>
+  </si>
+  <si>
+    <t>Liệt kê history mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Search lệnh chuyển tiền theo mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Search lệnh chuyển tiền có mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Kiểm tra history mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Search history với mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Xem chi tiết biến động số dư tại mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Cho tôi xem giao dịch với mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Cho tôi xem biến động số dư theo mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Tra cứu biến động số dư với mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Kiểm tra lệnh chuyển tiền có mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Kiểm tra biến động số dư với mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Cho tôi xem lệnh chuyển tiền tại mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Liệt kê lệnh chuyển tiền với mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Hiển thị history với mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}
+Xem chi tiết biến động số dư mang mã chi nhánh quản lý tài khoản đích. {{{to_account_branch}}}</t>
+  </si>
+  <si>
+    <t>Lọc các giao dịch với loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Những biến động số dư tại loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Những history mang loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Các history với loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Danh sách lệnh chuyển tiền có loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Các biến động số dư mang loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Các lệnh chuyển tiền theo loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Những biến động số dư với loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Danh sách lệnh chuyển tiền của loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Lọc các lệnh chuyển tiền mang loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Những giao dịch tại loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Danh sách history có loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Những giao dịch của loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Những lệnh chuyển tiền tại loại tiền tệ tài khoản đích. {{{to_account_currency}}}
+Danh sách biến động số dư với loại tiền tệ tài khoản đích. {{{to_account_currency}}}</t>
+  </si>
+  <si>
+    <t>Tính tổng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}
+Tính tổng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}
+Tổng cộng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}
+Thống kê số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}
+Cộng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng sau khi quy đổi tỷ giá nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng sau khi quy đổi tỷ giá nếu có theo trans_type {{trans_type}}
+Xem tổng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thực tế ghi có vào tài khoản nhận theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}
+Tính tổng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}
+Tổng cộng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}
+Thống kê số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}
+Cộng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng số tiền giao dịch gốc của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền giao dịch gốc theo trans_type {{trans_type}}
+Xem tổng số tiền nhập chuyển của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập chuyển theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng loại tiền tệ số tiền giao dịch. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ số tiền giao dịch. theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Các biến động số dư có tỷ giá quy đổi được áp dụng cho giao dịch {{{amount_rate}}}
+Lọc các biến động số dư theo tỷ giá quy đổi được áp dụng cho giao dịch {{{amount_rate}}}
+Danh sách giao dịch tại nếu chuyển đổi tiền tệ {{{amount_rate}}}
+Những giao dịch với tỷ giá quy đổi được áp dụng cho giao dịch {{{amount_rate}}}
+Các giao dịch mang số tiền {{{amount_rate}}}
+Những lệnh chuyển tiền theo số tiền {{{amount_rate}}}
+Các biến động số dư tại số tiền {{{amount_rate}}}
+Lọc các lệnh chuyển tiền tại số tiền {{{amount_rate}}}
+Những history tại giá trị {{{amount_rate}}}
+Lọc các lệnh chuyển tiền theo hạn mức {{{amount_rate}}}
+Lọc các giao dịch theo nếu chuyển đổi tiền tệ {{{amount_rate}}}
+Các biến động số dư có số tiền {{{amount_rate}}}
+Những lệnh chuyển tiền theo nếu chuyển đổi tiền tệ {{{amount_rate}}}
+Những biến động số dư của hạn mức {{{amount_rate}}}
+Những giao dịch có số tiền {{{amount_rate}}}</t>
+  </si>
+  <si>
+    <t>Tính tổng hold của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hold theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}
+Tổng cộng hold của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hold theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}
+Thống kê hold của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hold theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}
+Cộng hold của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hold theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}
+Xem tổng hold của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hold theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng số tiền bị phong tỏa của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền bị phong tỏa theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Kiểm tra biến động số dư của số tiền {{{block_amount_ref_no}}}
+Tìm biến động số dư theo giá trị {{{block_amount_ref_no}}}
+Cho tôi xem biến động số dư với số tiền {{{block_amount_ref_no}}}
+Tìm history có số tiền {{{block_amount_ref_no}}}
+Tra cứu biến động số dư có hạn mức {{{block_amount_ref_no}}}
+Kiểm tra biến động số dư có giá trị {{{block_amount_ref_no}}}
+Tra cứu biến động số dư với giá trị {{{block_amount_ref_no}}}
+giá trị {{{block_amount_ref_no}}} là bao nhiêu
+Hiển thị giao dịch mang giá trị {{{block_amount_ref_no}}}
+Search biến động số dư với số tiền {{{block_amount_ref_no}}}
+Tìm lệnh chuyển tiền với mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}
+Xem chi tiết giao dịch của giá trị {{{block_amount_ref_no}}}
+Hiển thị history có mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}
+Search history của số tiền {{{block_amount_ref_no}}}
+Liệt kê giao dịch tại mã tham chiếu lệnh phong tỏa tiền. {{{block_amount_ref_no}}}</t>
+  </si>
+  <si>
+    <t>Tính tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tính tổng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}
+Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}
+Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Tính tổng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}
+Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tổng cộng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}
+Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}
+Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Tổng cộng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}
+Thống kê phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Thống kê người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}
+Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}
+Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Thống kê đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}
+Cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Cộng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}
+Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}
+Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Cộng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}
+Xem tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Xem tổng người chuyển trả sender hay nhận trả receiver của các giao dịch có trans_type là {{trans_type}}
+Xem tổng người chuyển trả sender hay nhận trả receiver theo trans_type {{trans_type}}
+Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Xem tổng đối tượng chịu phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng đối tượng chịu phí theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}
+Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}
+Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}
+Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}
+Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng tổng số tiền phí dịch vụ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tổng số tiền phí dịch vụ. theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tính tổng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}
+Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tổng cộng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}
+Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Thống kê phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Thống kê loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}
+Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Cộng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}
+Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Xem tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Xem tổng loại tiền tệ phí. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng loại tiền tệ phí. theo trans_type {{trans_type}}
+Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}
+Tính tổng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}
+Tính tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}
+Tổng cộng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}
+Tổng cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}
+Thống kê tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}
+Thống kê tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}
+Cộng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}
+Cộng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu loại tiền phí khác loại tiền tài khoản theo trans_type {{trans_type}}
+Xem tổng tỷ giá quy đổi phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tỷ giá quy đổi phí theo trans_type {{trans_type}}
+Xem tổng tiền phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng tiền phí theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng phí của các giao dịch có trans_type là {{trans_type}}
+Xem tổng phí theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tìm biến động số dư theo tiền phí {{{fee_ind}}}
+Hiển thị giao dịch của chỉ số hoặc mã loại phí. {{{fee_ind}}}
+Xem chi tiết history theo phí {{{fee_ind}}}
+Hiển thị history của phí {{{fee_ind}}}
+Xem chi tiết lệnh chuyển tiền theo phí {{{fee_ind}}}
+phí {{{fee_ind}}} là bao nhiêu
+Cho tôi xem biến động số dư của phí {{{fee_ind}}}
+Search giao dịch theo phí {{{fee_ind}}}
+Kiểm tra history của tiền phí {{{fee_ind}}}
+Xem chi tiết lệnh chuyển tiền của chỉ số hoặc mã loại phí. {{{fee_ind}}}
+Liệt kê lệnh chuyển tiền của tiền phí {{{fee_ind}}}
+Liệt kê biến động số dư có phí {{{fee_ind}}}
+Tìm giao dịch với chỉ số hoặc mã loại phí. {{{fee_ind}}}
+Tra cứu lệnh chuyển tiền theo chỉ số hoặc mã loại phí. {{{fee_ind}}}
+Xem chi tiết history có phí {{{fee_ind}}}</t>
+  </si>
+  <si>
+    <t>Tính tổng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}
+Tính tổng nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu có theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}
+Tổng cộng nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu có theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}
+Thống kê nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu có theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}
+Cộng nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu có theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền hoa hồng trả cho đại lý/đối tác theo trans_type {{trans_type}}
+Xem tổng nếu có của các giao dịch có trans_type là {{trans_type}}
+Xem tổng nếu có theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Lọc các history theo loại tiền tệ hoa hồng. {{{commission_currency}}}
+Những history của loại tiền tệ hoa hồng. {{{commission_currency}}}
+Danh sách giao dịch tại loại tiền tệ hoa hồng. {{{commission_currency}}}
+Những giao dịch mang loại tiền tệ hoa hồng. {{{commission_currency}}}
+Danh sách history với loại tiền tệ hoa hồng. {{{commission_currency}}}
+Những biến động số dư theo loại tiền tệ hoa hồng. {{{commission_currency}}}
+Lọc các giao dịch có loại tiền tệ hoa hồng. {{{commission_currency}}}
+Danh sách history mang loại tiền tệ hoa hồng. {{{commission_currency}}}
+Lọc các biến động số dư của loại tiền tệ hoa hồng. {{{commission_currency}}}
+Danh sách giao dịch theo loại tiền tệ hoa hồng. {{{commission_currency}}}
+Những giao dịch có loại tiền tệ hoa hồng. {{{commission_currency}}}
+Các lệnh chuyển tiền với loại tiền tệ hoa hồng. {{{commission_currency}}}
+Những lệnh chuyển tiền với loại tiền tệ hoa hồng. {{{commission_currency}}}
+Các giao dịch có loại tiền tệ hoa hồng. {{{commission_currency}}}
+Lọc các giao dịch tại loại tiền tệ hoa hồng. {{{commission_currency}}}</t>
+  </si>
+  <si>
+    <t>Cho tôi xem lệnh chuyển tiền tại chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Hiển thị lệnh chuyển tiền với chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Kiểm tra giao dịch tại chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Tra cứu biến động số dư tại chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Kiểm tra biến động số dư theo chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Search biến động số dư mang chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Hiển thị biến động số dư của chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Xem chi tiết history có chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Xem chi tiết giao dịch theo chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Kiểm tra lệnh chuyển tiền với chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Search giao dịch có chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Liệt kê biến động số dư có chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Tra cứu lệnh chuyển tiền của chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Search history có chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}
+Tìm biến động số dư tại chỉ số hoặc mã loại hoa hồng. {{{commission_ind}}}</t>
+  </si>
+  <si>
+    <t>Kiểm tra biến động số dư của số tiền {{{promotion_amount}}}
+Tìm biến động số dư theo giá trị {{{promotion_amount}}}
+Cho tôi xem biến động số dư với số tiền {{{promotion_amount}}}
+Tìm history có số tiền {{{promotion_amount}}}
+Tra cứu biến động số dư có hạn mức {{{promotion_amount}}}
+Kiểm tra biến động số dư có giá trị {{{promotion_amount}}}
+Kiểm tra giao dịch tại số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}
+Tra cứu biến động số dư với giá trị {{{promotion_amount}}}
+giá trị {{{promotion_amount}}} là bao nhiêu
+Hiển thị giao dịch mang giá trị {{{promotion_amount}}}
+Search biến động số dư với số tiền {{{promotion_amount}}}
+Xem chi tiết giao dịch của giá trị {{{promotion_amount}}}
+Search history của số tiền {{{promotion_amount}}}
+Liệt kê giao dịch theo số tiền được khuyến mãi/giảm giá trực tiếp. {{{promotion_amount}}}
+Liệt kê history tại hạn mức {{{promotion_amount}}}</t>
+  </si>
+  <si>
+    <t>Cho tôi xem history với loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Tra cứu giao dịch mang loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Search history theo loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Liệt kê giao dịch của loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Cho tôi xem history có loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Hiển thị biến động số dư có loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Tra cứu biến động số dư mang loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Kiểm tra biến động số dư theo loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Liệt kê lệnh chuyển tiền mang loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Kiểm tra history với loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Liệt kê lệnh chuyển tiền với loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Kiểm tra lệnh chuyển tiền với loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Hiển thị biến động số dư của loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Tra cứu biến động số dư tại loại tiền tệ khuyến mãi. {{{promotion_currency}}}
+Tìm history của loại tiền tệ khuyến mãi. {{{promotion_currency}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị giao dịch với tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Kiểm tra history có tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Tìm giao dịch với tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Kiểm tra giao dịch tại tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Hiển thị biến động số dư có tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Liệt kê giao dịch mang tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Kiểm tra lệnh chuyển tiền của tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Xem chi tiết giao dịch theo tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Tra cứu biến động số dư của tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Xem chi tiết giao dịch mang tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Xem chi tiết lệnh chuyển tiền với tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Kiểm tra giao dịch của tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Tra cứu giao dịch mang tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Liệt kê biến động số dư mang tỷ lệ khuyến mãi. {{{promotion_rate}}}
+Hiển thị history của tỷ lệ khuyến mãi. {{{promotion_rate}}}</t>
+  </si>
+  <si>
+    <t>Liệt kê biến động số dư có chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Cho tôi xem giao dịch theo chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Liệt kê history có chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Xem chi tiết history của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Search lệnh chuyển tiền có chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Hiển thị lệnh chuyển tiền theo chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Cho tôi xem history của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Tìm biến động số dư với chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Xem chi tiết giao dịch của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Xem chi tiết biến động số dư có chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Liệt kê history mang chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Tra cứu biến động số dư của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Cho tôi xem history với chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Tra cứu history tại chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}
+Kiểm tra giao dịch của chỉ số hoặc mã chương trình khuyến mãi. {{{promotion_ind}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu lệnh chuyển tiền có số tham chiếu giao dịch {{{trans_ref_no}}}
+Kiểm tra biến động số dư tại reference number {{{trans_ref_no}}}
+Hiển thị lệnh chuyển tiền của số tham chiếu giao dịch {{{trans_ref_no}}}
+Liệt kê history theo reference number {{{trans_ref_no}}}
+Kiểm tra history có số tham chiếu giao dịch {{{trans_ref_no}}}
+Cho tôi xem giao dịch theo số tham chiếu giao dịch {{{trans_ref_no}}}
+Liệt kê lệnh chuyển tiền có reference number {{{trans_ref_no}}}
+Hiển thị biến động số dư với số tham chiếu giao dịch {{{trans_ref_no}}}
+Liệt kê giao dịch theo số tham chiếu giao dịch {{{trans_ref_no}}}
+Liệt kê history của reference number {{{trans_ref_no}}}
+Hiển thị history tại reference number {{{trans_ref_no}}}
+Tra cứu giao dịch tại số tham chiếu giao dịch {{{trans_ref_no}}}
+Cho tôi xem history có reference number {{{trans_ref_no}}}
+Xem chi tiết giao dịch có reference number {{{trans_ref_no}}}
+Cho tôi xem giao dịch theo reference number {{{trans_ref_no}}}</t>
+  </si>
+  <si>
+    <t>Danh sách giao dịch mang tương tự channel_receiver {{{request_channel}}}
+Lọc các giao dịch của kênh {{{request_channel}}}
+Những history theo nguồn {{{request_channel}}}
+Các history có nguồn {{{request_channel}}}
+Lọc các giao dịch theo nguồn {{{request_channel}}}
+Các giao dịch theo tương tự channel_receiver {{{request_channel}}}
+Lọc các history tại nguồn {{{request_channel}}}
+Lọc các lệnh chuyển tiền của kênh gửi yêu cầu {{{request_channel}}}
+Lọc các giao dịch của tương tự channel_receiver {{{request_channel}}}
+Lọc các history của nguồn {{{request_channel}}}
+Danh sách history với nguồn {{{request_channel}}}
+Danh sách giao dịch có nguồn {{{request_channel}}}
+Các history tại nguồn {{{request_channel}}}
+Những biến động số dư mang tương tự channel_receiver {{{request_channel}}}
+Lọc các giao dịch với kênh {{{request_channel}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị lệnh chuyển tiền tại nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Liệt kê history mang nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Search biến động số dư có nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Kiểm tra biến động số dư theo số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}
+Xem chi tiết lệnh chuyển tiền theo số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}
+Kiểm tra history tại nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Tra cứu giao dịch theo nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Liệt kê biến động số dư của nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Cho tôi xem history với số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}
+Tra cứu history với số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}
+Cho tôi xem giao dịch tại nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Kiểm tra lệnh chuyển tiền có nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Cho tôi xem biến động số dư với số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}
+Kiểm tra history mang nếu giao dịch này giao dịch hoàn {{{trans_revert_ref_no}}}
+Cho tôi xem lệnh chuyển tiền có số tham chiếu giao dịch hoàn tiền/đảo ngược {{{trans_revert_ref_no}}}</t>
+  </si>
+  <si>
+    <t>Tìm history với ví dụ: vnpay, momo, zalopay {{{partner_code}}}
+Cho tôi xem giao dịch tại mã đối tác tích hợp {{{partner_code}}}
+Kiểm tra giao dịch theo mã đối tác tích hợp {{{partner_code}}}
+Kiểm tra lệnh chuyển tiền của mã đối tác tích hợp {{{partner_code}}}
+Tìm lệnh chuyển tiền tại mã đối tác tích hợp {{{partner_code}}}
+Tra cứu lệnh chuyển tiền của mã đối tác tích hợp {{{partner_code}}}
+Tra cứu history tại ví dụ: vnpay, momo, zalopay {{{partner_code}}}
+Cho tôi xem lệnh chuyển tiền có ví dụ: vnpay, momo, zalopay {{{partner_code}}}
+Kiểm tra giao dịch với ví dụ: vnpay, momo, zalopay {{{partner_code}}}
+Tra cứu giao dịch có mã đối tác tích hợp {{{partner_code}}}
+Tra cứu history theo ví dụ: vnpay, momo, zalopay {{{partner_code}}}
+Hiển thị lệnh chuyển tiền theo mã đối tác tích hợp {{{partner_code}}}
+Tìm biến động số dư tại ví dụ: vnpay, momo, zalopay {{{partner_code}}}
+Liệt kê lệnh chuyển tiền có ví dụ: vnpay, momo, zalopay {{{partner_code}}}
+Liệt kê giao dịch tại ví dụ: vnpay, momo, zalopay {{{partner_code}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu giao dịch của ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+Xem chi tiết history theo ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+Kiểm tra biến động số dư của mã phản hồi từ {{{response_code}}}
+Hiển thị lệnh chuyển tiền có ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+Cho tôi xem history mang ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+Hiển thị giao dịch của mã phản hồi từ {{{response_code}}}
+Tìm history mang ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+Liệt kê lệnh chuyển tiền có ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+mã phản hồi từ {{{response_code}}} là bao nhiêu
+Hiển thị lệnh chuyển tiền tại mã phản hồi từ {{{response_code}}}
+Search history tại ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+Cho tôi xem history của mã phản hồi từ {{{response_code}}}
+Liệt kê lệnh chuyển tiền mang mã phản hồi từ {{{response_code}}}
+Kiểm tra lệnh chuyển tiền theo ví dụ: 00 - thành công, 01 - lỗi chung {{{response_code}}}
+Tìm history mang mã phản hồi từ {{{response_code}}}</t>
+  </si>
+  <si>
+    <t>Những lệnh chuyển tiền mang kết quả {{{response_status}}}
+Lọc các biến động số dư của trạng thái {{{response_status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{response_status}}}
+Những lệnh chuyển tiền theo ví dụ: s - success, f - fail {{{response_status}}}
+Các giao dịch của ví dụ: s - success, f - fail {{{response_status}}}
+Lọc các giao dịch theo ví dụ: s - success, f - fail {{{response_status}}}
+Những biến động số dư theo tình trạng {{{response_status}}}
+Danh sách biến động số dư của trạng thái {{{response_status}}}
+Những giao dịch của kết quả {{{response_status}}}
+Danh sách giao dịch theo kết quả {{{response_status}}}
+Các lệnh chuyển tiền của tình trạng {{{response_status}}}
+Lọc các history theo trạng thái phản hồi ngắn gọn {{{response_status}}}
+Danh sách biến động số dư có ví dụ: s - success, f - fail {{{response_status}}}
+Các history của trạng thái phản hồi ngắn gọn {{{response_status}}}
+Các giao dịch mang tình trạng {{{response_status}}}</t>
+  </si>
+  <si>
+    <t>Kiểm tra history của dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}
+Cho tôi xem history tại mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Search giao dịch của dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}
+Tìm giao dịch theo mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Tìm history của mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Tìm history mang dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}
+Tìm lệnh chuyển tiền với mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Tra cứu lệnh chuyển tiền theo dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}
+Kiểm tra biến động số dư với mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Search giao dịch của mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Liệt kê biến động số dư với dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}
+Hiển thị biến động số dư của mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Search lệnh chuyển tiền có mã lỗi kỹ thuật chi tiết {{{error_code}}}
+Xem chi tiết history mang dùng cho đội kỹ thuật tra cứu lỗi {{{error_code}}}
+Xem chi tiết giao dịch với mã lỗi kỹ thuật chi tiết {{{error_code}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{checker_id}}}
+Tra cứu giao dịch tại mã {{{checker_id}}}
+Kiểm tra biến động số dư có id duyệt giao dịch {{{checker_id}}}
+Kiểm tra biến động số dư có mã {{{checker_id}}}
+Liệt kê giao dịch tại id duyệt giao dịch {{{checker_id}}}
+Tra cứu giao dịch của số {{{checker_id}}}
+Cho tôi xem giao dịch với id {{{checker_id}}}
+Tra cứu biến động số dư theo số {{{checker_id}}}
+Liệt kê lệnh chuyển tiền theo id duyệt giao dịch {{{checker_id}}}
+Hiển thị giao dịch mang id {{{checker_id}}}
+Tra cứu giao dịch tại số {{{checker_id}}}
+Tra cứu history với kiểm soát viên {{{checker_id}}}
+Tìm biến động số dư tại id duyệt giao dịch {{{checker_id}}}
+Search biến động số dư theo id duyệt giao dịch {{{checker_id}}}
+Tìm biến động số dư có kiểm soát viên {{{checker_id}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{maker_id}}}
+Tra cứu giao dịch tại mã {{{maker_id}}}
+Tra cứu giao dịch có giao dịch viên {{{maker_id}}}
+Kiểm tra biến động số dư có mã {{{maker_id}}}
+Tra cứu giao dịch của số {{{maker_id}}}
+Cho tôi xem giao dịch với id {{{maker_id}}}
+Tra cứu biến động số dư theo số {{{maker_id}}}
+Tra cứu lệnh chuyển tiền của id tạo lệnh giao dịch {{{maker_id}}}
+Hiển thị giao dịch mang id {{{maker_id}}}
+Tra cứu giao dịch tại số {{{maker_id}}}
+Xem chi tiết giao dịch tại id tạo lệnh giao dịch {{{maker_id}}}
+Search lệnh chuyển tiền với id tạo lệnh giao dịch {{{maker_id}}}
+Tìm biến động số dư với số {{{maker_id}}}
+Tra cứu biến động số dư của id tạo lệnh giao dịch {{{maker_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{maker_id}}}</t>
+  </si>
+  <si>
+    <t>Các history tại trạng thái phê duyệt {{{approve_status}}}
+Danh sách biến động số dư với ví dụ: a - approved, r - rejected, p - pending {{{approve_status}}}
+Lọc các biến động số dư của trạng thái {{{approve_status}}}
+Những lệnh chuyển tiền mang kết quả {{{approve_status}}}
+Các giao dịch có trạng thái phê duyệt {{{approve_status}}}
+Những history của trạng thái phê duyệt {{{approve_status}}}
+Những biến động số dư theo trạng thái phê duyệt {{{approve_status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{approve_status}}}
+Danh sách history có ví dụ: a - approved, r - rejected, p - pending {{{approve_status}}}
+Các lệnh chuyển tiền có ví dụ: a - approved, r - rejected, p - pending {{{approve_status}}}
+Những biến động số dư theo tình trạng {{{approve_status}}}
+Lọc các history với ví dụ: a - approved, r - rejected, p - pending {{{approve_status}}}
+Danh sách biến động số dư của trạng thái {{{approve_status}}}
+Những giao dịch của kết quả {{{approve_status}}}
+Danh sách giao dịch theo kết quả {{{approve_status}}}</t>
+  </si>
+  <si>
+    <t>Các history theo thành công/thất bại/chờ xử lý/timeout {{{trans_status}}}
+Những lệnh chuyển tiền mang kết quả {{{trans_status}}}
+Lọc các biến động số dư của trạng thái {{{trans_status}}}
+Danh sách history theo trạng thái cuối cùng giao dịch {{{trans_status}}}
+Các giao dịch của thành công/thất bại/chờ xử lý/timeout {{{trans_status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{trans_status}}}
+Các biến động số dư mang trạng thái cuối cùng giao dịch {{{trans_status}}}
+Lọc các giao dịch với trạng thái cuối cùng giao dịch {{{trans_status}}}
+Những biến động số dư theo tình trạng {{{trans_status}}}
+Danh sách biến động số dư của trạng thái {{{trans_status}}}
+Những giao dịch của kết quả {{{trans_status}}}
+Các lệnh chuyển tiền của thành công/thất bại/chờ xử lý/timeout {{{trans_status}}}
+Lọc các biến động số dư tại trạng thái cuối cùng giao dịch {{{trans_status}}}
+Các giao dịch với thành công/thất bại/chờ xử lý/timeout {{{trans_status}}}
+Danh sách giao dịch theo kết quả {{{trans_status}}}</t>
+  </si>
+  <si>
+    <t>Kiểm tra biến động số dư tại số bút toán {{{core_ref_no}}}
+Hiển thị lệnh chuyển tiền có số bút toán {{{core_ref_no}}}
+Tra cứu history của ft id {{{core_ref_no}}}
+Tra cứu lệnh chuyển tiền có ft id {{{core_ref_no}}}
+Liệt kê giao dịch tại ft id {{{core_ref_no}}}
+Cho tôi xem lệnh chuyển tiền tại số bút toán {{{core_ref_no}}}
+Tra cứu history mang ft id {{{core_ref_no}}}
+Cho tôi xem history của ft id {{{core_ref_no}}}
+Tra cứu history có số bút toán {{{core_ref_no}}}
+Liệt kê giao dịch theo ft id {{{core_ref_no}}}
+Tra cứu lệnh chuyển tiền theo số bút toán {{{core_ref_no}}}
+Liệt kê history của ft id {{{core_ref_no}}}
+Liệt kê biến động số dư với số bút toán {{{core_ref_no}}}
+Tra cứu biến động số dư mang số bút toán {{{core_ref_no}}}
+Tra cứu giao dịch của ft id {{{core_ref_no}}}</t>
+  </si>
+  <si>
+    <t>Tra cứu history của số bút toán đảo core banking {{{core_revert_ref_no}}}
+Kiểm tra biến động số dư mang nếu có {{{core_revert_ref_no}}}
+Tìm lệnh chuyển tiền có số bút toán đảo core banking {{{core_revert_ref_no}}}
+Kiểm tra lệnh chuyển tiền theo số bút toán đảo core banking {{{core_revert_ref_no}}}
+Kiểm tra lệnh chuyển tiền tại số bút toán đảo core banking {{{core_revert_ref_no}}}
+Liệt kê lệnh chuyển tiền theo số bút toán đảo core banking {{{core_revert_ref_no}}}
+Xem chi tiết history của số bút toán đảo core banking {{{core_revert_ref_no}}}
+Tra cứu history với số bút toán đảo core banking {{{core_revert_ref_no}}}
+Liệt kê history theo nếu có {{{core_revert_ref_no}}}
+Liệt kê biến động số dư của nếu có {{{core_revert_ref_no}}}
+Xem chi tiết lệnh chuyển tiền theo nếu có {{{core_revert_ref_no}}}
+Search history tại số bút toán đảo core banking {{{core_revert_ref_no}}}
+Liệt kê lệnh chuyển tiền tại số bút toán đảo core banking {{{core_revert_ref_no}}}
+Hiển thị history theo nếu có {{{core_revert_ref_no}}}
+Liệt kê giao dịch theo số bút toán đảo core banking {{{core_revert_ref_no}}}</t>
+  </si>
+  <si>
+    <t>Cho tôi xem history mang mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Tra cứu biến động số dư tại mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Tra cứu giao dịch của mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Cho tôi xem lệnh chuyển tiền tại mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Kiểm tra history mang mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Tra cứu giao dịch tại mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Cho tôi xem giao dịch của mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Hiển thị history với mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Liệt kê history với mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Xem chi tiết biến động số dư mang mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Xem chi tiết giao dịch có mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Search lệnh chuyển tiền của mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Xem chi tiết giao dịch theo mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Cho tôi xem history theo mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}
+Xem chi tiết biến động số dư tại mã giao dịch tham chiếu tại cổng thanh toán. {{{payment_ref_no}}}</t>
+  </si>
+  <si>
+    <t>Những lệnh chuyển tiền mang kết quả {{{payment_status}}}
+Lọc các biến động số dư của trạng thái {{{payment_status}}}
+Danh sách giao dịch theo trạng thái trả về từ cổng thanh toán. {{{payment_status}}}
+Lọc các lệnh chuyển tiền mang kết quả {{{payment_status}}}
+Những biến động số dư theo tình trạng {{{payment_status}}}
+Những history mang trạng thái trả về từ cổng thanh toán. {{{payment_status}}}
+Danh sách biến động số dư của trạng thái {{{payment_status}}}
+Những giao dịch của kết quả {{{payment_status}}}
+Danh sách giao dịch theo kết quả {{{payment_status}}}
+Danh sách history tại trạng thái trả về từ cổng thanh toán. {{{payment_status}}}
+Các lệnh chuyển tiền của tình trạng {{{payment_status}}}
+Các giao dịch mang tình trạng {{{payment_status}}}
+Lọc các history với kết quả {{{payment_status}}}
+Lọc các lệnh chuyển tiền của kết quả {{{payment_status}}}
+Những biến động số dư có kết quả {{{payment_status}}}</t>
+  </si>
+  <si>
+    <t>Search history tại ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}
+Cho tôi xem lệnh chuyển tiền có mã khách hàng trên hóa đơn {{{bill_customer_code}}}
+Cho tôi xem giao dịch tại ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}
+Kiểm tra history mang mã khách hàng trên hóa đơn {{{bill_customer_code}}}
+Search giao dịch mang mã khách hàng trên hóa đơn {{{bill_customer_code}}}
+Search lệnh chuyển tiền theo ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}
+Search history có ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}
+Cho tôi xem history tại mã khách hàng trên hóa đơn {{{bill_customer_code}}}
+Cho tôi xem lệnh chuyển tiền của mã khách hàng trên hóa đơn {{{bill_customer_code}}}
+Hiển thị biến động số dư có ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}
+Cho tôi xem biến động số dư theo ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}
+Cho tôi xem lệnh chuyển tiền mang ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}
+Kiểm tra history của mã khách hàng trên hóa đơn {{{bill_customer_code}}}
+Tra cứu giao dịch có mã khách hàng trên hóa đơn {{{bill_customer_code}}}
+Tra cứu giao dịch mang ví dụ: mã danh bộ nước, mã khách hàng điện lực {{{bill_customer_code}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{bill_id}}}
+Tra cứu biến động số dư mang mã định danh hóa đơn hệ thống. {{{bill_id}}}
+Tra cứu giao dịch tại mã {{{bill_id}}}
+Kiểm tra biến động số dư có mã {{{bill_id}}}
+Tra cứu giao dịch của số {{{bill_id}}}
+Tìm history tại mã định danh hóa đơn hệ thống. {{{bill_id}}}
+Cho tôi xem giao dịch với id {{{bill_id}}}
+Tra cứu biến động số dư theo số {{{bill_id}}}
+Hiển thị giao dịch mang id {{{bill_id}}}
+Tra cứu giao dịch tại số {{{bill_id}}}
+Tìm biến động số dư với số {{{bill_id}}}
+Liệt kê lệnh chuyển tiền mang mã định danh hóa đơn hệ thống. {{{bill_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{bill_id}}}
+mã {{{bill_id}}} là bao nhiêu
+Search biến động số dư theo mã {{{bill_id}}}</t>
+  </si>
+  <si>
+    <t>Các giao dịch của hình thức {{{bill_type}}}
+Danh sách lệnh chuyển tiền có loại hóa đơn {{{bill_type}}}
+Danh sách giao dịch tại điện, nước, internet, truyền hình... {{{bill_type}}}
+Các lệnh chuyển tiền theo hình thức {{{bill_type}}}
+Các lệnh chuyển tiền tại hình thức {{{bill_type}}}
+Các giao dịch mang loại {{{bill_type}}}
+Lọc các biến động số dư có loại hóa đơn {{{bill_type}}}
+Các giao dịch tại loại {{{bill_type}}}
+Những history có điện, nước, internet, truyền hình... {{{bill_type}}}
+Những lệnh chuyển tiền theo loại hóa đơn {{{bill_type}}}
+Những giao dịch mang loại {{{bill_type}}}
+Lọc các biến động số dư của loại {{{bill_type}}}
+Những biến động số dư của điện, nước, internet, truyền hình... {{{bill_type}}}
+Lọc các giao dịch mang loại {{{bill_type}}}
+Các biến động số dư theo loại {{{bill_type}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị biến động số dư có mã tra cứu hóa đơn. {{{bill_code}}}
+Cho tôi xem lệnh chuyển tiền của mã tra cứu hóa đơn. {{{bill_code}}}
+Tìm biến động số dư mang mã tra cứu hóa đơn. {{{bill_code}}}
+Liệt kê history có mã tra cứu hóa đơn. {{{bill_code}}}
+Search lệnh chuyển tiền tại mã tra cứu hóa đơn. {{{bill_code}}}
+Kiểm tra history của mã tra cứu hóa đơn. {{{bill_code}}}
+Liệt kê giao dịch của mã tra cứu hóa đơn. {{{bill_code}}}
+Tra cứu history theo mã tra cứu hóa đơn. {{{bill_code}}}
+Kiểm tra lệnh chuyển tiền theo mã tra cứu hóa đơn. {{{bill_code}}}
+Tra cứu giao dịch có mã tra cứu hóa đơn. {{{bill_code}}}
+Tìm lệnh chuyển tiền tại mã tra cứu hóa đơn. {{{bill_code}}}
+Hiển thị giao dịch mang mã tra cứu hóa đơn. {{{bill_code}}}
+Search biến động số dư có mã tra cứu hóa đơn. {{{bill_code}}}
+Cho tôi xem giao dịch có mã tra cứu hóa đơn. {{{bill_code}}}
+Kiểm tra giao dịch với mã tra cứu hóa đơn. {{{bill_code}}}</t>
+  </si>
+  <si>
+    <t>Những giao dịch mang loại tiền tệ hóa đơn. {{{bill_currency}}}
+Những history tại loại tiền tệ hóa đơn. {{{bill_currency}}}
+Danh sách giao dịch có loại tiền tệ hóa đơn. {{{bill_currency}}}
+Những giao dịch theo loại tiền tệ hóa đơn. {{{bill_currency}}}
+Những giao dịch của loại tiền tệ hóa đơn. {{{bill_currency}}}
+Danh sách history của loại tiền tệ hóa đơn. {{{bill_currency}}}
+Lọc các giao dịch mang loại tiền tệ hóa đơn. {{{bill_currency}}}
+Các biến động số dư của loại tiền tệ hóa đơn. {{{bill_currency}}}
+Những lệnh chuyển tiền theo loại tiền tệ hóa đơn. {{{bill_currency}}}
+Lọc các lệnh chuyển tiền tại loại tiền tệ hóa đơn. {{{bill_currency}}}
+Các biến động số dư mang loại tiền tệ hóa đơn. {{{bill_currency}}}
+Các history của loại tiền tệ hóa đơn. {{{bill_currency}}}
+Những lệnh chuyển tiền với loại tiền tệ hóa đơn. {{{bill_currency}}}
+Danh sách biến động số dư mang loại tiền tệ hóa đơn. {{{bill_currency}}}
+Danh sách history mang loại tiền tệ hóa đơn. {{{bill_currency}}}</t>
+  </si>
+  <si>
+    <t>Tính tổng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}
+Tổng cộng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}
+Thống kê số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}
+Cộng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}
+Xem tổng số tiền chiết khấu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng thường thanh toán hóa đơn của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường thanh toán hóa đơn theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}
+Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}
+Tính tổng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}
+Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}
+Tổng cộng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}
+Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}
+Thống kê số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}
+Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}
+Cộng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng trước khi tính phí/thuế của các giao dịch có trans_type là {{trans_type}}
+Xem tổng trước khi tính phí/thuế theo trans_type {{trans_type}}
+Xem tổng số tiền nhập vào ban đầu của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền nhập vào ban đầu theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thuế vat theo trans_type {{trans_type}}
+Tổng cộng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thuế vat theo trans_type {{trans_type}}
+Thống kê thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thuế vat theo trans_type {{trans_type}}
+Cộng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thuế vat theo trans_type {{trans_type}}
+Xem tổng thường tính trên phí dịch vụ của các giao dịch có trans_type là {{trans_type}}
+Xem tổng thường tính trên phí dịch vụ theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng số tiền thuế vat của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền thuế vat theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Tính tổng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}
+Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền chiết khấu do đối tác tài trợ. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền chiết khấu do đối tác tài trợ. theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết biến động số dư tại số {{{server_session_id}}}
+Tra cứu giao dịch tại mã {{{server_session_id}}}
+Kiểm tra biến động số dư có mã {{{server_session_id}}}
+Tra cứu giao dịch của số {{{server_session_id}}}
+Cho tôi xem giao dịch với id {{{server_session_id}}}
+Tra cứu biến động số dư theo số {{{server_session_id}}}
+Hiển thị giao dịch mang id {{{server_session_id}}}
+Tra cứu giao dịch tại số {{{server_session_id}}}
+Hiển thị history mang backend session {{{server_session_id}}}
+Tìm biến động số dư với số {{{server_session_id}}}
+Liệt kê lệnh chuyển tiền của mã {{{server_session_id}}}
+mã {{{server_session_id}}} là bao nhiêu
+Search history với mã phiên làm việc phía server {{{server_session_id}}}
+Tra cứu giao dịch tại mã phiên làm việc phía server {{{server_session_id}}}
+Tra cứu lệnh chuyển tiền tại mã {{{server_session_id}}}</t>
+  </si>
+  <si>
+    <t>Các giao dịch của hình thức {{{source_type}}}
+Những history có ví dụ: account - tài khoản thanh toán, card - thẻ, ewallet - ví {{{source_type}}}
+Các lệnh chuyển tiền theo hình thức {{{source_type}}}
+Các lệnh chuyển tiền tại hình thức {{{source_type}}}
+Các giao dịch của loại nguồn tiền {{{source_type}}}
+Các giao dịch mang loại {{{source_type}}}
+Các biến động số dư mang loại nguồn tiền {{{source_type}}}
+Các giao dịch tại loại {{{source_type}}}
+Những giao dịch mang loại {{{source_type}}}
+Lọc các biến động số dư của loại {{{source_type}}}
+Lọc các giao dịch mang loại {{{source_type}}}
+Lọc các lệnh chuyển tiền theo loại nguồn tiền {{{source_type}}}
+Các biến động số dư theo loại {{{source_type}}}
+Danh sách giao dịch theo loại nguồn tiền {{{source_type}}}
+Danh sách giao dịch mang loại nguồn tiền {{{source_type}}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết lệnh chuyển tiền mang số thẻ {{{card_number}}}
+Search giao dịch mang số thẻ {{{card_number}}}
+Xem chi tiết biến động số dư theo số thẻ {{{card_number}}}
+Liệt kê biến động số dư tại thường được mã hóa hoặc che bớt số {{{card_number}}}
+Xem chi tiết lệnh chuyển tiền tại thường được mã hóa hoặc che bớt số {{{card_number}}}
+Tìm lệnh chuyển tiền của số thẻ {{{card_number}}}
+Xem chi tiết giao dịch với thường được mã hóa hoặc che bớt số {{{card_number}}}
+Kiểm tra giao dịch tại số thẻ {{{card_number}}}
+Liệt kê giao dịch theo số thẻ {{{card_number}}}
+Liệt kê history theo số thẻ {{{card_number}}}
+Cho tôi xem giao dịch của số thẻ {{{card_number}}}
+Hiển thị giao dịch với thường được mã hóa hoặc che bớt số {{{card_number}}}
+Cho tôi xem lệnh chuyển tiền có thường được mã hóa hoặc che bớt số {{{card_number}}}
+Cho tôi xem lệnh chuyển tiền có số thẻ {{{card_number}}}
+Tra cứu history mang số thẻ {{{card_number}}}</t>
+  </si>
+  <si>
+    <t>Hiển thị biến động số dư của mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Cho tôi xem history có digital operation {{{cust_no_do}}}
+Cho tôi xem biến động số dư có digital operation {{{cust_no_do}}}
+Tra cứu giao dịch mang digital operation {{{cust_no_do}}}
+Cho tôi xem lệnh chuyển tiền của mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Cho tôi xem biến động số dư tại mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Cho tôi xem giao dịch tại digital operation {{{cust_no_do}}}
+Kiểm tra history theo mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Hiển thị giao dịch theo mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Hiển thị biến động số dư mang mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Kiểm tra giao dịch mang mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Hiển thị biến động số dư có mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Xem chi tiết history tại digital operation {{{cust_no_do}}}
+Search giao dịch của mã khách hàng tác nghiệp số {{{cust_no_do}}}
+Tìm lệnh chuyển tiền theo digital operation {{{cust_no_do}}}</t>
+  </si>
+  <si>
+    <t>Tính tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tính tổng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}
+Tính tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tính tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Tổng cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Tổng cộng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}
+Tổng cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Tổng cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Thống kê số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Thống kê giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}
+Thống kê hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Thống kê giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Cộng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Cộng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}
+Cộng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Cộng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}
+Xem tổng số tiền của các giao dịch có trans_type là {{trans_type}}
+Xem tổng số tiền theo trans_type {{trans_type}}
+Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị tiền ghi trên hóa đơn cần thanh toán. theo trans_type {{trans_type}}
+Xem tổng hạn mức của các giao dịch có trans_type là {{trans_type}}
+Xem tổng hạn mức theo trans_type {{trans_type}}
+Xem tổng giá trị của các giao dịch có trans_type là {{trans_type}}
+Xem tổng giá trị theo trans_type {{trans_type}}</t>
+  </si>
+  <si>
+    <t>Xem chi tiết giao dịch của dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}
+Xem chi tiết history theo dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}
+Tra cứu history với mã danh mục giao dịch {{{category_code}}}
+Tìm giao dịch theo mã danh mục giao dịch {{{category_code}}}
+Xem chi tiết biến động số dư tại mã danh mục giao dịch {{{category_code}}}
+Xem chi tiết history theo mã danh mục giao dịch {{{category_code}}}
+Search giao dịch mang dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}
+Search biến động số dư của dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}
+Cho tôi xem history của dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}
+Liệt kê biến động số dư với mã danh mục giao dịch {{{category_code}}}
+Tìm biến động số dư mang dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}
+Tìm giao dịch tại dùng phân loại chi tiêu, ví dụ: "ăn uống", "đi lại" {{{category_code}}}
+Search giao dịch của mã danh mục giao dịch {{{category_code}}}
+Search history có mã danh mục giao dịch {{{category_code}}}
+Xem chi tiết giao dịch theo mã danh mục giao dịch {{{category_code}}}</t>
+  </si>
+  <si>
+    <t>Cho tôi xem giao dịch với customer information file {{{from_cif_no}}}
+Cho tôi xem lệnh chuyển tiền với mã cif {{{from_cif_no}}}
+Liệt kê lệnh chuyển tiền có tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}
+Cho tôi xem giao dịch của customer information file {{{from_cif_no}}}
+Tra cứu biến động số dư có tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}
+Liệt kê giao dịch với mã cif {{{from_cif_no}}}
+Kiểm tra lệnh chuyển tiền với mã cif {{{from_cif_no}}}
+Kiểm tra history tại tương tự from_cust_no nhưng thường định danh core banking {{{from_cif_no}}}
+Liệt kê history với mã cif {{{from_cif_no}}}
+Tìm history có customer information file {{{from_cif_no}}}
+Xem chi tiết history với mã cif {{{from_cif_no}}}
+Tìm lệnh chuyển tiền với mã cif {{{from_cif_no}}}
+Tìm biến động số dư với customer information file {{{from_cif_no}}}
+Search lệnh chuyển tiền với mã cif {{{from_cif_no}}}
+Xem chi tiết history với customer information file {{{from_cif_no}}}</t>
   </si>
   <si>
     <t>reference_id, tra cứu, tìm kiếm</t>
@@ -1348,8 +2979,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1401,10 +3032,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1412,13 +3049,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1456,7 +3101,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1490,6 +3135,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1524,9 +3170,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1699,18 +3346,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E94"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="34.61328125" customWidth="1"/>
+    <col min="2" max="2" width="45.07421875" customWidth="1"/>
+    <col min="3" max="3" width="255.69140625" style="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1720,14 +3372,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>98</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>182</v>
       </c>
       <c r="D2" t="s">
@@ -1737,14 +3389,14 @@
         <v>350</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>99</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>183</v>
       </c>
       <c r="D3" t="s">
@@ -1754,14 +3406,14 @@
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>100</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>184</v>
       </c>
       <c r="D4" t="s">
@@ -1771,14 +3423,14 @@
         <v>352</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>101</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D5" t="s">
@@ -1788,14 +3440,14 @@
         <v>353</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>102</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>186</v>
       </c>
       <c r="D6" t="s">
@@ -1805,14 +3457,14 @@
         <v>354</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>103</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D7" t="s">
@@ -1822,14 +3474,14 @@
         <v>355</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>104</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>188</v>
       </c>
       <c r="D8" t="s">
@@ -1839,14 +3491,14 @@
         <v>356</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>105</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D9" t="s">
@@ -1856,14 +3508,14 @@
         <v>357</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>106</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>190</v>
       </c>
       <c r="D10" t="s">
@@ -1873,14 +3525,14 @@
         <v>358</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>107</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>191</v>
       </c>
       <c r="D11" t="s">
@@ -1890,14 +3542,14 @@
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>108</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>192</v>
       </c>
       <c r="D12" t="s">
@@ -1907,14 +3559,14 @@
         <v>360</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>193</v>
       </c>
       <c r="D13" t="s">
@@ -1924,14 +3576,14 @@
         <v>361</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>110</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>194</v>
       </c>
       <c r="D14" t="s">
@@ -1941,14 +3593,14 @@
         <v>362</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>111</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D15" t="s">
@@ -1958,14 +3610,14 @@
         <v>363</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>112</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>196</v>
       </c>
       <c r="D16" t="s">
@@ -1975,14 +3627,14 @@
         <v>364</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>113</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>197</v>
       </c>
       <c r="D17" t="s">
@@ -1992,14 +3644,14 @@
         <v>365</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>114</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="3" t="s">
         <v>198</v>
       </c>
       <c r="D18" t="s">
@@ -2009,14 +3661,14 @@
         <v>366</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>115</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>199</v>
       </c>
       <c r="D19" t="s">
@@ -2026,14 +3678,14 @@
         <v>367</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>116</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>200</v>
       </c>
       <c r="D20" t="s">
@@ -2043,14 +3695,14 @@
         <v>368</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>117</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>201</v>
       </c>
       <c r="D21" t="s">
@@ -2060,14 +3712,14 @@
         <v>369</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>118</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>202</v>
       </c>
       <c r="D22" t="s">
@@ -2077,14 +3729,14 @@
         <v>370</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>119</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>203</v>
       </c>
       <c r="D23" t="s">
@@ -2094,14 +3746,14 @@
         <v>371</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>120</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>204</v>
       </c>
       <c r="D24" t="s">
@@ -2111,14 +3763,14 @@
         <v>372</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>121</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>205</v>
       </c>
       <c r="D25" t="s">
@@ -2128,14 +3780,14 @@
         <v>373</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>122</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
         <v>206</v>
       </c>
       <c r="D26" t="s">
@@ -2145,14 +3797,14 @@
         <v>374</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>123</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D27" t="s">
@@ -2162,14 +3814,14 @@
         <v>375</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>124</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>208</v>
       </c>
       <c r="D28" t="s">
@@ -2179,14 +3831,14 @@
         <v>376</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>125</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>209</v>
       </c>
       <c r="D29" t="s">
@@ -2196,14 +3848,14 @@
         <v>377</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>126</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>210</v>
       </c>
       <c r="D30" t="s">
@@ -2213,14 +3865,14 @@
         <v>378</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>127</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="3" t="s">
         <v>211</v>
       </c>
       <c r="D31" t="s">
@@ -2230,14 +3882,14 @@
         <v>379</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>128</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>212</v>
       </c>
       <c r="D32" t="s">
@@ -2247,14 +3899,14 @@
         <v>380</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>129</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>213</v>
       </c>
       <c r="D33" t="s">
@@ -2264,14 +3916,14 @@
         <v>381</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>130</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D34" t="s">
@@ -2281,14 +3933,14 @@
         <v>382</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
         <v>131</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>215</v>
       </c>
       <c r="D35" t="s">
@@ -2298,14 +3950,14 @@
         <v>383</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>132</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>216</v>
       </c>
       <c r="D36" t="s">
@@ -2315,14 +3967,14 @@
         <v>384</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>133</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
         <v>217</v>
       </c>
       <c r="D37" t="s">
@@ -2332,14 +3984,14 @@
         <v>385</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
         <v>134</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D38" t="s">
@@ -2349,14 +4001,14 @@
         <v>386</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>135</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D39" t="s">
@@ -2366,14 +4018,14 @@
         <v>387</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
         <v>136</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>220</v>
       </c>
       <c r="D40" t="s">
@@ -2383,14 +4035,14 @@
         <v>388</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>137</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>221</v>
       </c>
       <c r="D41" t="s">
@@ -2400,14 +4052,14 @@
         <v>389</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>222</v>
       </c>
       <c r="D42" t="s">
@@ -2417,14 +4069,14 @@
         <v>390</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
         <v>139</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="3" t="s">
         <v>223</v>
       </c>
       <c r="D43" t="s">
@@ -2434,14 +4086,14 @@
         <v>391</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>140</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
         <v>224</v>
       </c>
       <c r="D44" t="s">
@@ -2451,14 +4103,14 @@
         <v>392</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
         <v>141</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="3" t="s">
         <v>225</v>
       </c>
       <c r="D45" t="s">
@@ -2468,14 +4120,14 @@
         <v>393</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
         <v>142</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="3" t="s">
         <v>226</v>
       </c>
       <c r="D46" t="s">
@@ -2485,14 +4137,14 @@
         <v>394</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
         <v>143</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="3" t="s">
         <v>227</v>
       </c>
       <c r="D47" t="s">
@@ -2502,14 +4154,14 @@
         <v>395</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
         <v>144</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="3" t="s">
         <v>228</v>
       </c>
       <c r="D48" t="s">
@@ -2519,14 +4171,14 @@
         <v>396</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
         <v>145</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="3" t="s">
         <v>229</v>
       </c>
       <c r="D49" t="s">
@@ -2536,14 +4188,14 @@
         <v>397</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
         <v>146</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>230</v>
       </c>
       <c r="D50" t="s">
@@ -2553,14 +4205,14 @@
         <v>398</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
         <v>147</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="3" t="s">
         <v>231</v>
       </c>
       <c r="D51" t="s">
@@ -2570,14 +4222,14 @@
         <v>399</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
         <v>148</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="3" t="s">
         <v>232</v>
       </c>
       <c r="D52" t="s">
@@ -2587,14 +4239,14 @@
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
         <v>149</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="3" t="s">
         <v>233</v>
       </c>
       <c r="D53" t="s">
@@ -2604,14 +4256,14 @@
         <v>401</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
         <v>150</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="3" t="s">
         <v>234</v>
       </c>
       <c r="D54" t="s">
@@ -2621,14 +4273,14 @@
         <v>402</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
         <v>151</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="3" t="s">
         <v>235</v>
       </c>
       <c r="D55" t="s">
@@ -2638,14 +4290,14 @@
         <v>403</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
         <v>105</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D56" t="s">
@@ -2655,14 +4307,14 @@
         <v>404</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
         <v>152</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D57" t="s">
@@ -2672,14 +4324,14 @@
         <v>405</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
         <v>153</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="3" t="s">
         <v>237</v>
       </c>
       <c r="D58" t="s">
@@ -2689,14 +4341,14 @@
         <v>406</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
         <v>154</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="3" t="s">
         <v>238</v>
       </c>
       <c r="D59" t="s">
@@ -2706,14 +4358,14 @@
         <v>407</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
         <v>105</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D60" t="s">
@@ -2723,14 +4375,14 @@
         <v>408</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
         <v>155</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="3" t="s">
         <v>239</v>
       </c>
       <c r="D61" t="s">
@@ -2740,14 +4392,14 @@
         <v>409</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>156</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="3" t="s">
         <v>240</v>
       </c>
       <c r="D62" t="s">
@@ -2757,14 +4409,14 @@
         <v>410</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
         <v>157</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="3" t="s">
         <v>241</v>
       </c>
       <c r="D63" t="s">
@@ -2774,14 +4426,14 @@
         <v>411</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
         <v>158</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="3" t="s">
         <v>242</v>
       </c>
       <c r="D64" t="s">
@@ -2791,14 +4443,14 @@
         <v>412</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
         <v>105</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D65" t="s">
@@ -2808,14 +4460,14 @@
         <v>413</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
         <v>159</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="3" t="s">
         <v>243</v>
       </c>
       <c r="D66" t="s">
@@ -2825,14 +4477,14 @@
         <v>414</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
         <v>105</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D67" t="s">
@@ -2842,14 +4494,14 @@
         <v>415</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
         <v>160</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="3" t="s">
         <v>244</v>
       </c>
       <c r="D68" t="s">
@@ -2859,14 +4511,14 @@
         <v>416</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
         <v>161</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="3" t="s">
         <v>245</v>
       </c>
       <c r="D69" t="s">
@@ -2876,14 +4528,14 @@
         <v>417</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
         <v>162</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="3" t="s">
         <v>246</v>
       </c>
       <c r="D70" t="s">
@@ -2893,14 +4545,14 @@
         <v>418</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
         <v>163</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="3" t="s">
         <v>247</v>
       </c>
       <c r="D71" t="s">
@@ -2910,14 +4562,14 @@
         <v>419</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
         <v>164</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="3" t="s">
         <v>248</v>
       </c>
       <c r="D72" t="s">
@@ -2927,14 +4579,14 @@
         <v>420</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
         <v>165</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="3" t="s">
         <v>249</v>
       </c>
       <c r="D73" t="s">
@@ -2944,14 +4596,14 @@
         <v>421</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
         <v>166</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="3" t="s">
         <v>250</v>
       </c>
       <c r="D74" t="s">
@@ -2961,14 +4613,14 @@
         <v>422</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
         <v>167</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>251</v>
       </c>
       <c r="D75" t="s">
@@ -2978,14 +4630,14 @@
         <v>423</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
         <v>168</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="3" t="s">
         <v>252</v>
       </c>
       <c r="D76" t="s">
@@ -2995,14 +4647,14 @@
         <v>424</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
         <v>169</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="3" t="s">
         <v>253</v>
       </c>
       <c r="D77" t="s">
@@ -3012,14 +4664,14 @@
         <v>425</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
         <v>170</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="3" t="s">
         <v>254</v>
       </c>
       <c r="D78" t="s">
@@ -3029,14 +4681,14 @@
         <v>426</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
         <v>105</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D79" t="s">
@@ -3046,14 +4698,14 @@
         <v>427</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
         <v>105</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D80" t="s">
@@ -3063,14 +4715,14 @@
         <v>428</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
         <v>105</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D81" t="s">
@@ -3080,14 +4732,14 @@
         <v>429</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
         <v>105</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D82" t="s">
@@ -3097,14 +4749,14 @@
         <v>430</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
         <v>171</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="3" t="s">
         <v>255</v>
       </c>
       <c r="D83" t="s">
@@ -3114,14 +4766,14 @@
         <v>431</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
         <v>172</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="3" t="s">
         <v>256</v>
       </c>
       <c r="D84" t="s">
@@ -3131,14 +4783,14 @@
         <v>432</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
         <v>105</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="3" t="s">
         <v>189</v>
       </c>
       <c r="D85" t="s">
@@ -3148,14 +4800,14 @@
         <v>433</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
         <v>173</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="3" t="s">
         <v>257</v>
       </c>
       <c r="D86" t="s">
@@ -3165,14 +4817,14 @@
         <v>434</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
         <v>174</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="3" t="s">
         <v>258</v>
       </c>
       <c r="D87" t="s">
@@ -3182,14 +4834,14 @@
         <v>435</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
         <v>175</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="3" t="s">
         <v>259</v>
       </c>
       <c r="D88" t="s">
@@ -3199,14 +4851,14 @@
         <v>436</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
         <v>176</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="3" t="s">
         <v>260</v>
       </c>
       <c r="D89" t="s">
@@ -3216,14 +4868,14 @@
         <v>437</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
         <v>177</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="3" t="s">
         <v>261</v>
       </c>
       <c r="D90" t="s">
@@ -3233,14 +4885,14 @@
         <v>438</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
         <v>178</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="3" t="s">
         <v>262</v>
       </c>
       <c r="D91" t="s">
@@ -3250,14 +4902,14 @@
         <v>439</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" ht="409.6" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
         <v>179</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="3" t="s">
         <v>263</v>
       </c>
       <c r="D92" t="s">
@@ -3267,14 +4919,14 @@
         <v>440</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
         <v>180</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="3" t="s">
         <v>264</v>
       </c>
       <c r="D93" t="s">
@@ -3284,14 +4936,14 @@
         <v>441</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="218.6" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
         <v>181</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="3" t="s">
         <v>265</v>
       </c>
       <c r="D94" t="s">
